--- a/project-earlobe/finance/cost-model.xlsx
+++ b/project-earlobe/finance/cost-model.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="346">
   <si>
     <t xml:space="preserve">Project Earlobe — cost-out &amp; ROI model (Curious &amp; Creative Network)</t>
   </si>
@@ -164,7 +164,25 @@
     <t xml:space="preserve">credits</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0 for highest-quality voices; some faster models bill ~0.5 (F-TTS) — verify per model</t>
+    <t xml:space="preserve">1.0 full-quality voices; Flash/Turbo ~0.5 (F-TTS-09) — verify per model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-render / QA overhead on voice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(inference) F-TTS-16: retakes, pronunciation fixes, QA listens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secondary voice engine, $ per audio minute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Chirp 3 HD-class, $30 per 1M chars (F-TTS-23)</t>
   </si>
   <si>
     <t xml:space="preserve">Weekdays per month</t>
@@ -197,9 +215,6 @@
     <t xml:space="preserve">Cost of one rewrite loop vs a first pass</t>
   </si>
   <si>
-    <t xml:space="preserve">x</t>
-  </si>
-  <si>
     <t xml:space="preserve">(inference) writer + re-check of changed claims</t>
   </si>
   <si>
@@ -383,6 +398,12 @@
     <t xml:space="preserve">Overage, $ per 1k extra credits</t>
   </si>
   <si>
+    <t xml:space="preserve">Share of minutes on secondary engine (hybrid)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ElevenLabs Startup Grant credits / month (0 unless awarded)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Revenue rates by case</t>
   </si>
   <si>
@@ -401,16 +422,19 @@
     <t xml:space="preserve">Programmatic CPM (gross, per 1,000 ad impressions)</t>
   </si>
   <si>
-    <t xml:space="preserve">$</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ad fill rate</t>
   </si>
   <si>
     <t xml:space="preserve">Our share after host/marketplace</t>
   </si>
   <si>
-    <t xml:space="preserve">Local sponsor, $ per show per month</t>
+    <t xml:space="preserve">Local direct sponsor, effective CPM per slot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local sponsor slots sold (sell-through)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flat community package, $ per month</t>
   </si>
   <si>
     <t xml:space="preserve">B2B white-label brief, $ per client per month</t>
@@ -434,7 +458,7 @@
     <t xml:space="preserve">Driver</t>
   </si>
   <si>
-    <t xml:space="preserve">Local sponsors per local/courts show</t>
+    <t xml:space="preserve">Community packages sold per local/courts show</t>
   </si>
   <si>
     <t xml:space="preserve">B2B white-label clients</t>
@@ -572,7 +596,7 @@
     <t xml:space="preserve">Audio minutes / month</t>
   </si>
   <si>
-    <t xml:space="preserve">Voice credits needed / month</t>
+    <t xml:space="preserve">ElevenLabs credits needed / month (after hybrid share, overhead, grant)</t>
   </si>
   <si>
     <t xml:space="preserve">ElevenLabs plan price</t>
@@ -587,7 +611,7 @@
     <t xml:space="preserve">Voice (ElevenLabs) cost / month</t>
   </si>
   <si>
-    <t xml:space="preserve">Effective $ per voice credit</t>
+    <t xml:space="preserve">Effective voice $ per audio minute</t>
   </si>
   <si>
     <t xml:space="preserve">Claude API (agents + web search) / month</t>
@@ -608,7 +632,7 @@
     <t xml:space="preserve">Programmatic ad revenue</t>
   </si>
   <si>
-    <t xml:space="preserve">Local sponsors (local + courts shows)</t>
+    <t xml:space="preserve">Local sponsors (impressions sold + community packages)</t>
   </si>
   <si>
     <t xml:space="preserve">B2B white-label briefs</t>
@@ -713,13 +737,13 @@
     <t xml:space="preserve">Podcast hosting + dynamic ad insertion</t>
   </si>
   <si>
-    <t xml:space="preserve">Multi-show host (see cost-analysis.md)</t>
+    <t xml:space="preserve">Multi-show host (see cost-out-and-roi.md)</t>
   </si>
   <si>
     <t xml:space="preserve">monthly</t>
   </si>
   <si>
-    <t xml:space="preserve">Plan tiers scale with downloads/shows (F-HOST) — verify</t>
+    <t xml:space="preserve">F-HOST-10 — verify current plans</t>
   </si>
   <si>
     <t xml:space="preserve">Insurance</t>
@@ -728,10 +752,10 @@
     <t xml:space="preserve">Media liability / E&amp;O</t>
   </si>
   <si>
-    <t xml:space="preserve">Online insurer quote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insureon avg ~$78/mo; larger limits at scale (F-LEGAL)</t>
+    <t xml:space="preserve">Specialist media insurer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-LEGAL-01 placeholder; automated courts/crime may be declined — get quotes</t>
   </si>
   <si>
     <t xml:space="preserve">Infrastructure</t>
@@ -752,7 +776,7 @@
     <t xml:space="preserve">Free → Pro</t>
   </si>
   <si>
-    <t xml:space="preserve">Free tier at test; set to 25 for Pro</t>
+    <t xml:space="preserve">Free tier pauses when idle; Pro from Wave 1 (F-INFRA-03)</t>
   </si>
   <si>
     <t xml:space="preserve">Compute for always-on agents / runners</t>
@@ -767,25 +791,49 @@
     <t xml:space="preserve">Data</t>
   </si>
   <si>
-    <t xml:space="preserve">News/search data APIs beyond RSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e.g. news API, court data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(inference) RSS, GDELT, CourtListener free tiers first (F-DATA)</t>
+    <t xml:space="preserve">Court + news data (PACER, paid APIs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PACER, CourtListener, news API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-DATA-02 PACER ~$150-300/mo; CourtListener/GDELT free first</t>
   </si>
   <si>
     <t xml:space="preserve">Voice</t>
   </si>
   <si>
-    <t xml:space="preserve">Google AI Pro (NotebookLM, optional)</t>
+    <t xml:space="preserve">Google AI Pro (NotebookLM, optional prototyping)</t>
   </si>
   <si>
     <t xml:space="preserve">Google AI Pro</t>
   </si>
   <si>
-    <t xml:space="preserve">Optional; prototyping only (F-TTS)</t>
+    <t xml:space="preserve">Not a production engine (F-TTS-32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">California LLC annual tax (if CA-registered)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franchise Tax Board</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$800/yr (F-LEGAL-05)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Music</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Music / sonic library license</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Library subscription</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-LEGAL-06</t>
   </si>
   <si>
     <t xml:space="preserve">Admin</t>
@@ -839,25 +887,28 @@
     <t xml:space="preserve">Note / source</t>
   </si>
   <si>
-    <t xml:space="preserve">Legal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media-lawyer consult on standards + courts/crime lanes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(inference) 3–5 hrs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trademark: 'Curious &amp; Creative Network' (2 classes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USPTO $350/class (F-LEGAL)</t>
+    <t xml:space="preserve">Media-lawyer setup review (standards, courts/crime lanes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-LEGAL-02 mid ($2,500-$7,500)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trademark filing: 2 classes (41, then 9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USPTO $350/class (F-LEGAL-03)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trademark clearance search (attorney)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-LEGAL-02 ($500-$2,000 per mark)</t>
   </si>
   <si>
     <t xml:space="preserve">DBA / assumed-name filing</t>
   </si>
   <si>
-    <t xml:space="preserve">Varies by state/county (F-LEGAL)</t>
+    <t xml:space="preserve">F-LEGAL-04 (~$56-$176)</t>
   </si>
   <si>
     <t xml:space="preserve">Brand</t>
@@ -1020,7 +1071,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
@@ -1030,7 +1081,6 @@
     <numFmt numFmtId="170" formatCode="#,##0.0;\(#,##0.0\);\-"/>
     <numFmt numFmtId="171" formatCode="0.0\x"/>
     <numFmt numFmtId="172" formatCode="\$#,##0.0000"/>
-    <numFmt numFmtId="173" formatCode="\$#,##0.000000"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -1188,7 +1238,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1294,10 +1344,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1772,19 +1818,19 @@
       <c r="B15" s="2"/>
       <c r="C15" s="6" t="n">
         <f aca="false">Scenarios!C37</f>
-        <v>43024</v>
+        <v>33982</v>
       </c>
       <c r="D15" s="6" t="n">
         <f aca="false">Scenarios!D37</f>
-        <v>158928</v>
+        <v>131109</v>
       </c>
       <c r="E15" s="6" t="n">
         <f aca="false">Scenarios!E37</f>
-        <v>874337.5</v>
+        <v>670680</v>
       </c>
       <c r="F15" s="6" t="n">
         <f aca="false">Scenarios!F37</f>
-        <v>4256910</v>
+        <v>3172200</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1794,19 +1840,19 @@
       <c r="B16" s="2"/>
       <c r="C16" s="7" t="n">
         <f aca="false">Scenarios!C33</f>
-        <v>653.400549031</v>
+        <v>1431.740549031</v>
       </c>
       <c r="D16" s="7" t="n">
         <f aca="false">Scenarios!D33</f>
-        <v>2052.627340187</v>
+        <v>2826.307340187</v>
       </c>
       <c r="E16" s="7" t="n">
         <f aca="false">Scenarios!E33</f>
-        <v>7093.393115096</v>
+        <v>8608.063115096</v>
       </c>
       <c r="F16" s="7" t="n">
         <f aca="false">Scenarios!F33</f>
-        <v>20772.251805247</v>
+        <v>27723.095805247</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1816,19 +1862,19 @@
       <c r="B17" s="2"/>
       <c r="C17" s="7" t="n">
         <f aca="false">Scenarios!C44</f>
-        <v>4015.8732</v>
+        <v>3848.55486</v>
       </c>
       <c r="D17" s="7" t="n">
         <f aca="false">Scenarios!D44</f>
-        <v>13203.3234</v>
+        <v>12263.18817</v>
       </c>
       <c r="E17" s="7" t="n">
         <f aca="false">Scenarios!E44</f>
-        <v>60812.165</v>
+        <v>48420.51275</v>
       </c>
       <c r="F17" s="7" t="n">
         <f aca="false">Scenarios!F44</f>
-        <v>275573.524</v>
+        <v>197817.1616</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1838,19 +1884,19 @@
       <c r="B18" s="2"/>
       <c r="C18" s="7" t="n">
         <f aca="false">Scenarios!C45</f>
-        <v>3362.472650969</v>
+        <v>2416.814310969</v>
       </c>
       <c r="D18" s="7" t="n">
         <f aca="false">Scenarios!D45</f>
-        <v>11150.696059813</v>
+        <v>9436.880829813</v>
       </c>
       <c r="E18" s="7" t="n">
         <f aca="false">Scenarios!E45</f>
-        <v>53718.771884904</v>
+        <v>39812.449634904</v>
       </c>
       <c r="F18" s="7" t="n">
         <f aca="false">Scenarios!F45</f>
-        <v>254801.272194753</v>
+        <v>170094.065794753</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1860,19 +1906,19 @@
       <c r="B19" s="2"/>
       <c r="C19" s="7" t="n">
         <f aca="false">Scenarios!C50</f>
-        <v>362.472650969</v>
+        <v>-583.185689031</v>
       </c>
       <c r="D19" s="7" t="n">
         <f aca="false">Scenarios!D50</f>
-        <v>3150.696059813</v>
+        <v>1436.880829813</v>
       </c>
       <c r="E19" s="7" t="n">
         <f aca="false">Scenarios!E50</f>
-        <v>30218.771884904</v>
+        <v>16312.449634904</v>
       </c>
       <c r="F19" s="7" t="n">
         <f aca="false">Scenarios!F50</f>
-        <v>180301.272194753</v>
+        <v>95594.065794753</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1890,7 +1936,7 @@
       <c r="B21" s="2"/>
       <c r="C21" s="6" t="n">
         <f aca="false">'12-Month Plan'!D20</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -1903,7 +1949,7 @@
       <c r="B22" s="2"/>
       <c r="C22" s="7" t="n">
         <f aca="false">'12-Month Plan'!D21</f>
-        <v>-3021.813229031</v>
+        <v>-9326.088731093</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -1916,7 +1962,7 @@
       <c r="B23" s="2"/>
       <c r="C23" s="8" t="n">
         <f aca="false">'12-Month Plan'!D24</f>
-        <v>4.49854663752885</v>
+        <v>2.29916976912599</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -1938,7 +1984,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M94"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -2159,7 +2205,7 @@
         <v>46</v>
       </c>
       <c r="B12" s="11" t="n">
-        <v>21.7</v>
+        <v>1.25</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>47</v>
@@ -2182,12 +2228,14 @@
         <v>49</v>
       </c>
       <c r="B13" s="11" t="n">
-        <v>30.4</v>
+        <v>0.03</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="2"/>
+        <v>50</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -2200,16 +2248,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="12" t="n">
-        <v>0.15</v>
+        <v>52</v>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>21.7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -2223,17 +2271,15 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>54</v>
-      </c>
+      <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -2246,16 +2292,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="11" t="n">
-        <v>0.6</v>
+        <v>56</v>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>0.15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -2269,16 +2315,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B17" s="12" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
@@ -2291,10 +2337,18 @@
       <c r="M17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -2306,12 +2360,18 @@
       <c r="M18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -2323,18 +2383,10 @@
       <c r="M19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>39</v>
-      </c>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -2346,18 +2398,12 @@
       <c r="M20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B21" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="C21" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="D21" s="2" t="s">
+      <c r="A21" s="4" t="s">
         <v>65</v>
       </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -2369,17 +2415,17 @@
       <c r="M21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B22" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C22" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>65</v>
+      <c r="B22" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -2393,16 +2439,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B23" s="13" t="n">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>0.5</v>
+        <v>20</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -2416,14 +2462,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B24" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
@@ -2436,10 +2484,18 @@
       <c r="M24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
+      <c r="A25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -2451,12 +2507,16 @@
       <c r="M25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B26" s="2"/>
+      <c r="A26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="13" t="n">
+        <v>10</v>
+      </c>
       <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
+      <c r="D26" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -2468,24 +2528,12 @@
       <c r="M26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>75</v>
-      </c>
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -2495,25 +2543,14 @@
       <c r="M27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" s="10" t="n">
-        <v>60000</v>
-      </c>
-      <c r="D28" s="10" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="15" t="n">
-        <f aca="false">C28/1000000*IF(B28="opus",Assumptions!$B$21,IF(B28="sonnet",Assumptions!$B$22,Assumptions!$B$23))+D28/1000000*IF(B28="opus",Assumptions!$C$21,IF(B28="sonnet",Assumptions!$C$22,Assumptions!$C$23))+E28/1000*Assumptions!$B$24</f>
-        <v>0.008</v>
-      </c>
+      <c r="A28" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -2523,24 +2560,23 @@
       <c r="M28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B29" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="10" t="n">
-        <v>40000</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <f aca="false">C29/1000000*IF(B29="opus",Assumptions!$B$21,IF(B29="sonnet",Assumptions!$B$22,Assumptions!$B$23))+D29/1000000*IF(B29="opus",Assumptions!$C$21,IF(B29="sonnet",Assumptions!$C$22,Assumptions!$C$23))+E29/1000*Assumptions!$B$24</f>
-        <v>0.36</v>
+      <c r="D29" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>80</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -2552,13 +2588,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>8000</v>
+        <v>60000</v>
       </c>
       <c r="D30" s="10" t="n">
         <v>4000</v>
@@ -2567,8 +2603,8 @@
         <v>0</v>
       </c>
       <c r="F30" s="15" t="n">
-        <f aca="false">C30/1000000*IF(B30="opus",Assumptions!$B$21,IF(B30="sonnet",Assumptions!$B$22,Assumptions!$B$23))+D30/1000000*IF(B30="opus",Assumptions!$C$21,IF(B30="sonnet",Assumptions!$C$22,Assumptions!$C$23))+E30/1000*Assumptions!$B$24</f>
-        <v>0.112</v>
+        <f aca="false">C30/1000000*IF(B30="opus",Assumptions!$B$23,IF(B30="sonnet",Assumptions!$B$24,Assumptions!$B$25))+D30/1000000*IF(B30="opus",Assumptions!$C$23,IF(B30="sonnet",Assumptions!$C$24,Assumptions!$C$25))+E30/1000*Assumptions!$B$26</f>
+        <v>0.008</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -2580,23 +2616,23 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>150000</v>
+        <v>40000</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F31" s="15" t="n">
-        <f aca="false">C31/1000000*IF(B31="opus",Assumptions!$B$21,IF(B31="sonnet",Assumptions!$B$22,Assumptions!$B$23))+D31/1000000*IF(B31="opus",Assumptions!$C$21,IF(B31="sonnet",Assumptions!$C$22,Assumptions!$C$23))+E31/1000*Assumptions!$B$24</f>
-        <v>1.04</v>
+        <f aca="false">C31/1000000*IF(B31="opus",Assumptions!$B$23,IF(B31="sonnet",Assumptions!$B$24,Assumptions!$B$25))+D31/1000000*IF(B31="opus",Assumptions!$C$23,IF(B31="sonnet",Assumptions!$C$24,Assumptions!$C$25))+E31/1000*Assumptions!$B$26</f>
+        <v>0.36</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -2608,23 +2644,23 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C32" s="10" t="n">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="15" t="n">
-        <f aca="false">C32/1000000*IF(B32="opus",Assumptions!$B$21,IF(B32="sonnet",Assumptions!$B$22,Assumptions!$B$23))+D32/1000000*IF(B32="opus",Assumptions!$C$21,IF(B32="sonnet",Assumptions!$C$22,Assumptions!$C$23))+E32/1000*Assumptions!$B$24</f>
-        <v>0.28</v>
+        <f aca="false">C32/1000000*IF(B32="opus",Assumptions!$B$23,IF(B32="sonnet",Assumptions!$B$24,Assumptions!$B$25))+D32/1000000*IF(B32="opus",Assumptions!$C$23,IF(B32="sonnet",Assumptions!$C$24,Assumptions!$C$25))+E32/1000*Assumptions!$B$26</f>
+        <v>0.112</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -2636,23 +2672,23 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C33" s="10" t="n">
-        <v>10000</v>
+        <v>150000</v>
       </c>
       <c r="D33" s="10" t="n">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F33" s="15" t="n">
-        <f aca="false">C33/1000000*IF(B33="opus",Assumptions!$B$21,IF(B33="sonnet",Assumptions!$B$22,Assumptions!$B$23))+D33/1000000*IF(B33="opus",Assumptions!$C$21,IF(B33="sonnet",Assumptions!$C$22,Assumptions!$C$23))+E33/1000*Assumptions!$B$24</f>
-        <v>0.05</v>
+        <f aca="false">C33/1000000*IF(B33="opus",Assumptions!$B$23,IF(B33="sonnet",Assumptions!$B$24,Assumptions!$B$25))+D33/1000000*IF(B33="opus",Assumptions!$C$23,IF(B33="sonnet",Assumptions!$C$24,Assumptions!$C$25))+E33/1000*Assumptions!$B$26</f>
+        <v>1.04</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -2664,23 +2700,23 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C34" s="10" t="n">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="E34" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="15" t="n">
-        <f aca="false">C34/1000000*IF(B34="opus",Assumptions!$B$21,IF(B34="sonnet",Assumptions!$B$22,Assumptions!$B$23))+D34/1000000*IF(B34="opus",Assumptions!$C$21,IF(B34="sonnet",Assumptions!$C$22,Assumptions!$C$23))+E34/1000*Assumptions!$B$24</f>
-        <v>0.1</v>
+        <f aca="false">C34/1000000*IF(B34="opus",Assumptions!$B$23,IF(B34="sonnet",Assumptions!$B$24,Assumptions!$B$25))+D34/1000000*IF(B34="opus",Assumptions!$C$23,IF(B34="sonnet",Assumptions!$C$24,Assumptions!$C$25))+E34/1000*Assumptions!$B$26</f>
+        <v>0.28</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -2692,13 +2728,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C35" s="10" t="n">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="D35" s="10" t="n">
         <v>3000</v>
@@ -2707,8 +2743,8 @@
         <v>0</v>
       </c>
       <c r="F35" s="15" t="n">
-        <f aca="false">C35/1000000*IF(B35="opus",Assumptions!$B$21,IF(B35="sonnet",Assumptions!$B$22,Assumptions!$B$23))+D35/1000000*IF(B35="opus",Assumptions!$C$21,IF(B35="sonnet",Assumptions!$C$22,Assumptions!$C$23))+E35/1000*Assumptions!$B$24</f>
-        <v>0.046</v>
+        <f aca="false">C35/1000000*IF(B35="opus",Assumptions!$B$23,IF(B35="sonnet",Assumptions!$B$24,Assumptions!$B$25))+D35/1000000*IF(B35="opus",Assumptions!$C$23,IF(B35="sonnet",Assumptions!$C$24,Assumptions!$C$25))+E35/1000*Assumptions!$B$26</f>
+        <v>0.05</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
@@ -2720,23 +2756,23 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="E36" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="15" t="n">
-        <f aca="false">C36/1000000*IF(B36="opus",Assumptions!$B$21,IF(B36="sonnet",Assumptions!$B$22,Assumptions!$B$23))+D36/1000000*IF(B36="opus",Assumptions!$C$21,IF(B36="sonnet",Assumptions!$C$22,Assumptions!$C$23))+E36/1000*Assumptions!$B$24</f>
-        <v>0.00135</v>
+        <f aca="false">C36/1000000*IF(B36="opus",Assumptions!$B$23,IF(B36="sonnet",Assumptions!$B$24,Assumptions!$B$25))+D36/1000000*IF(B36="opus",Assumptions!$C$23,IF(B36="sonnet",Assumptions!$C$24,Assumptions!$C$25))+E36/1000*Assumptions!$B$26</f>
+        <v>0.1</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -2747,16 +2783,24 @@
       <c r="M36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="16" t="n">
-        <f aca="false">SUM(F28:F36)</f>
-        <v>1.99735</v>
+      <c r="A37" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="15" t="n">
+        <f aca="false">C37/1000000*IF(B37="opus",Assumptions!$B$23,IF(B37="sonnet",Assumptions!$B$24,Assumptions!$B$25))+D37/1000000*IF(B37="opus",Assumptions!$C$23,IF(B37="sonnet",Assumptions!$C$24,Assumptions!$C$25))+E37/1000*Assumptions!$B$26</f>
+        <v>0.046</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
@@ -2767,12 +2811,25 @@
       <c r="M37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
+      <c r="A38" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="15" t="n">
+        <f aca="false">C38/1000000*IF(B38="opus",Assumptions!$B$23,IF(B38="sonnet",Assumptions!$B$24,Assumptions!$B$25))+D38/1000000*IF(B38="opus",Assumptions!$C$23,IF(B38="sonnet",Assumptions!$C$24,Assumptions!$C$25))+E38/1000*Assumptions!$B$26</f>
+        <v>0.00135</v>
+      </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
@@ -2783,13 +2840,16 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
+      <c r="F39" s="16" t="n">
+        <f aca="false">SUM(F30:F38)</f>
+        <v>1.99735</v>
+      </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
@@ -2798,28 +2858,14 @@
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
     </row>
-    <row r="40" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>93</v>
-      </c>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
@@ -2828,61 +2874,45 @@
       <c r="M40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B41" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="C41" s="17" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="D41" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G41" s="10" t="n">
-        <v>150</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>95</v>
-      </c>
+      <c r="A41" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
+    <row r="42" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B42" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C42" s="17" t="n">
-        <v>30</v>
-      </c>
-      <c r="D42" s="18" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="10" t="n">
-        <v>600</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>95</v>
-      </c>
+      <c r="F42" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -2891,16 +2921,16 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B43" s="10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C43" s="17" t="n">
         <v>21.7</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="E43" s="10" t="n">
         <v>0</v>
@@ -2912,7 +2942,7 @@
         <v>120</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
@@ -2922,28 +2952,28 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B44" s="10" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C44" s="17" t="n">
-        <v>8.3</v>
+        <v>30</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
@@ -2953,28 +2983,28 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B45" s="10" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C45" s="17" t="n">
-        <v>8.7</v>
+        <v>21.7</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
@@ -2984,28 +3014,28 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B46" s="10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C46" s="17" t="n">
-        <v>13</v>
+        <v>8.3</v>
       </c>
       <c r="D46" s="18" t="n">
         <v>1.8</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" s="10" t="n">
         <v>3</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
@@ -3015,28 +3045,28 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B47" s="10" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C47" s="17" t="n">
-        <v>12</v>
+        <v>8.7</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G47" s="10" t="n">
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
@@ -3045,14 +3075,30 @@
       <c r="M47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
+      <c r="A48" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="D48" s="18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G48" s="10" t="n">
+        <v>400</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
@@ -3060,16 +3106,30 @@
       <c r="M48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
+      <c r="A49" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B49" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C49" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="D49" s="18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
@@ -3077,21 +3137,11 @@
       <c r="M49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -3102,21 +3152,13 @@
       <c r="M50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B51" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C51" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="D51" s="19" t="n">
-        <v>25</v>
-      </c>
-      <c r="E51" s="19" t="n">
-        <v>100</v>
-      </c>
+      <c r="A51" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
@@ -3127,20 +3169,20 @@
       <c r="M51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B52" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D52" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="E52" s="19" t="n">
-        <v>5</v>
+      <c r="A52" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -3153,19 +3195,19 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B53" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53" s="19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D53" s="19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E53" s="19" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -3178,19 +3220,19 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B54" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C54" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" s="19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" s="19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -3203,19 +3245,19 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B55" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C55" s="19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D55" s="19" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E55" s="19" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -3228,19 +3270,19 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B56" s="19" t="n">
         <v>1</v>
       </c>
       <c r="C56" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" s="19" t="n">
         <v>4</v>
-      </c>
-      <c r="D56" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="E56" s="19" t="n">
-        <v>50</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
@@ -3253,19 +3295,19 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B57" s="19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C57" s="19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D57" s="19" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="E57" s="19" t="n">
-        <v>500</v>
+        <v>4</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -3278,19 +3320,19 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B58" s="18" t="n">
+        <v>105</v>
+      </c>
+      <c r="B58" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C58" s="18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D58" s="18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E58" s="18" t="n">
-        <v>3.5</v>
+      <c r="C58" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D58" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="E58" s="19" t="n">
+        <v>50</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -3302,11 +3344,21 @@
       <c r="M58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
+      <c r="A59" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B59" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D59" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E59" s="19" t="n">
+        <v>500</v>
+      </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
@@ -3317,13 +3369,21 @@
       <c r="M59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
+      <c r="A60" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B60" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D60" s="18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E60" s="18" t="n">
+        <v>3</v>
+      </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
@@ -3334,21 +3394,11 @@
       <c r="M60" s="2"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>39</v>
-      </c>
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
@@ -3359,22 +3409,13 @@
       <c r="M61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B62" s="20" t="n">
-        <v>22</v>
-      </c>
-      <c r="C62" s="10" t="n">
-        <v>121000</v>
-      </c>
-      <c r="D62" s="15" t="n">
-        <f aca="false">IF(C62=0,0,B62/C62*1000)</f>
-        <v>0.181818181818182</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>110</v>
-      </c>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
@@ -3385,21 +3426,20 @@
       <c r="M62" s="2"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B63" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B63" s="20" t="n">
-        <v>99</v>
-      </c>
-      <c r="C63" s="10" t="n">
-        <v>600000</v>
-      </c>
-      <c r="D63" s="15" t="n">
-        <f aca="false">IF(C63=0,0,B63/C63*1000)</f>
-        <v>0.165</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>110</v>
+      <c r="C63" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -3412,20 +3452,20 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>18</v>
+        <v>114</v>
       </c>
       <c r="B64" s="20" t="n">
-        <v>299</v>
+        <v>22</v>
       </c>
       <c r="C64" s="10" t="n">
-        <v>1800000</v>
+        <v>121000</v>
       </c>
       <c r="D64" s="15" t="n">
         <f aca="false">IF(C64=0,0,B64/C64*1000)</f>
-        <v>0.166111111111111</v>
+        <v>0.181818181818182</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -3438,20 +3478,20 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B65" s="20" t="n">
-        <v>990</v>
+        <v>99</v>
       </c>
       <c r="C65" s="10" t="n">
-        <v>6000000</v>
+        <v>600000</v>
       </c>
       <c r="D65" s="15" t="n">
         <f aca="false">IF(C65=0,0,B65/C65*1000)</f>
         <v>0.165</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
@@ -3464,20 +3504,20 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>113</v>
+        <v>18</v>
       </c>
       <c r="B66" s="20" t="n">
-        <v>3000</v>
+        <v>299</v>
       </c>
       <c r="C66" s="10" t="n">
-        <v>30000000</v>
+        <v>1800000</v>
       </c>
       <c r="D66" s="15" t="n">
         <f aca="false">IF(C66=0,0,B66/C66*1000)</f>
-        <v>0.1</v>
+        <v>0.166111111111111</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -3489,20 +3529,21 @@
       <c r="M66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="5" t="s">
+      <c r="A67" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B67" s="20" t="n">
+        <v>990</v>
+      </c>
+      <c r="C67" s="10" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="D67" s="15" t="n">
+        <f aca="false">IF(C67=0,0,B67/C67*1000)</f>
+        <v>0.165</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>19</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -3515,19 +3556,20 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="E68" s="9" t="s">
-        <v>113</v>
+        <v>118</v>
+      </c>
+      <c r="B68" s="20" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C68" s="10" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="D68" s="15" t="n">
+        <f aca="false">IF(C68=0,0,B68/C68*1000)</f>
+        <v>0.1</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -3539,20 +3581,20 @@
       <c r="M68" s="2"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B69" s="13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C69" s="13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D69" s="13" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E69" s="13" t="n">
-        <v>0.06</v>
+      <c r="A69" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -3564,11 +3606,21 @@
       <c r="M69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
+      <c r="A70" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>118</v>
+      </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
@@ -3579,13 +3631,21 @@
       <c r="M70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
+      <c r="A71" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B71" s="13" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C71" s="13" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D71" s="13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E71" s="13" t="n">
+        <v>0.1</v>
+      </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
@@ -3596,20 +3656,20 @@
       <c r="M71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>38</v>
+      <c r="A72" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="12" t="n">
+        <v>0</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -3622,19 +3682,19 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B73" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="C73" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="D73" s="20" t="n">
-        <v>22</v>
-      </c>
-      <c r="E73" s="2" t="s">
         <v>124</v>
+      </c>
+      <c r="B73" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -3646,21 +3706,11 @@
       <c r="M73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B74" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C74" s="12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D74" s="12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>51</v>
-      </c>
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
@@ -3671,21 +3721,13 @@
       <c r="M74" s="2"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B75" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C75" s="12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D75" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>51</v>
-      </c>
+      <c r="A75" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
@@ -3696,20 +3738,20 @@
       <c r="M75" s="2"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="s">
+      <c r="A76" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B76" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B76" s="20" t="n">
-        <v>300</v>
-      </c>
-      <c r="C76" s="20" t="n">
-        <v>750</v>
-      </c>
-      <c r="D76" s="20" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>124</v>
+      <c r="C76" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
@@ -3722,19 +3764,19 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B77" s="20" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="C77" s="20" t="n">
-        <v>2000</v>
+        <v>13</v>
       </c>
       <c r="D77" s="20" t="n">
-        <v>3500</v>
+        <v>20</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
@@ -3747,19 +3789,19 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B78" s="20" t="n">
-        <v>500</v>
-      </c>
-      <c r="C78" s="20" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D78" s="20" t="n">
-        <v>3000</v>
+        <v>131</v>
+      </c>
+      <c r="B78" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C78" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D78" s="12" t="n">
+        <v>0.75</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>124</v>
+        <v>57</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -3772,19 +3814,19 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B79" s="20" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C79" s="20" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D79" s="20" t="n">
-        <v>5000</v>
+        <v>132</v>
+      </c>
+      <c r="B79" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C79" s="12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D79" s="12" t="n">
+        <v>0.7</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>124</v>
+        <v>57</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -3797,19 +3839,19 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B80" s="20" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C80" s="20" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="D80" s="20" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
@@ -3822,14 +3864,20 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B81" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
+        <v>0.25</v>
+      </c>
+      <c r="C81" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D81" s="12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
@@ -3840,11 +3888,21 @@
       <c r="M81" s="2"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
+      <c r="A82" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B82" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="C82" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="D82" s="20" t="n">
+        <v>150</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
@@ -3855,13 +3913,21 @@
       <c r="M82" s="2"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
+      <c r="A83" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B83" s="20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C83" s="20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D83" s="20" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -3872,20 +3938,20 @@
       <c r="M83" s="2"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>19</v>
+      <c r="A84" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B84" s="20" t="n">
+        <v>500</v>
+      </c>
+      <c r="C84" s="20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D84" s="20" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
@@ -3898,19 +3964,19 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B85" s="17" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C85" s="17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D85" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" s="17" t="n">
-        <v>1.5</v>
+        <v>138</v>
+      </c>
+      <c r="B85" s="20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C85" s="20" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D85" s="20" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
@@ -3923,19 +3989,19 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B86" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" s="10" t="n">
+        <v>139</v>
+      </c>
+      <c r="B86" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C86" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="E86" s="10" t="n">
-        <v>20</v>
+      <c r="D86" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
@@ -3948,20 +4014,14 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B87" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C87" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>15</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="B87" s="12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
@@ -3972,21 +4032,11 @@
       <c r="M87" s="2"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B88" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C88" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D88" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>4</v>
-      </c>
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -3997,21 +4047,13 @@
       <c r="M88" s="2"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B89" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C89" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D89" s="10" t="n">
-        <v>500</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>3000</v>
-      </c>
+      <c r="A89" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -4022,11 +4064,21 @@
       <c r="M89" s="2"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2"/>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
+      <c r="A90" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -4037,13 +4089,21 @@
       <c r="M90" s="2"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
+      <c r="A91" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B91" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>4</v>
+      </c>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -4054,125 +4114,257 @@
       <c r="M91" s="2"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D92" s="5" t="s">
+      <c r="A92" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E92" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="G92" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="H92" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="I92" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="J92" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="K92" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="L92" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="M92" s="5" t="s">
-        <v>153</v>
-      </c>
+      <c r="B92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="2"/>
+      <c r="L92" s="2"/>
+      <c r="M92" s="2"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B93" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C93" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D93" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F93" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="G93" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H93" s="19" t="n">
+        <v>145</v>
+      </c>
+      <c r="B93" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I93" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J93" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K93" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="L93" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="M93" s="19" t="n">
-        <v>3</v>
-      </c>
+      <c r="E93" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2"/>
+      <c r="L93" s="2"/>
+      <c r="M93" s="2"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B94" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D94" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+      <c r="J94" s="2"/>
+      <c r="K94" s="2"/>
+      <c r="L94" s="2"/>
+      <c r="M94" s="2"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B95" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="D95" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2"/>
+      <c r="K95" s="2"/>
+      <c r="L95" s="2"/>
+      <c r="M95" s="2"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2"/>
+      <c r="L96" s="2"/>
+      <c r="M96" s="2"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="2"/>
+      <c r="K97" s="2"/>
+      <c r="L97" s="2"/>
+      <c r="M97" s="2"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="G98" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B94" s="12" t="n">
+      <c r="H98" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="I98" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="J98" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="K98" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="L98" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="M98" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B99" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F99" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G99" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H99" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I99" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J99" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K99" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L99" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M99" s="19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B100" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="C94" s="12" t="n">
+      <c r="C100" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="D94" s="12" t="n">
+      <c r="D100" s="12" t="n">
         <v>0.3</v>
       </c>
-      <c r="E94" s="12" t="n">
+      <c r="E100" s="12" t="n">
         <v>0.35</v>
       </c>
-      <c r="F94" s="12" t="n">
+      <c r="F100" s="12" t="n">
         <v>0.45</v>
       </c>
-      <c r="G94" s="12" t="n">
+      <c r="G100" s="12" t="n">
         <v>0.55</v>
       </c>
-      <c r="H94" s="12" t="n">
+      <c r="H100" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="I94" s="12" t="n">
+      <c r="I100" s="12" t="n">
         <v>0.6</v>
       </c>
-      <c r="J94" s="12" t="n">
+      <c r="J100" s="12" t="n">
         <v>0.7</v>
       </c>
-      <c r="K94" s="12" t="n">
+      <c r="K100" s="12" t="n">
         <v>0.8</v>
       </c>
-      <c r="L94" s="12" t="n">
+      <c r="L100" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="M94" s="12" t="n">
+      <c r="M100" s="12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4207,7 +4399,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4220,7 +4412,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4244,47 +4436,47 @@
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">Assumptions!B41</f>
+        <f aca="false">Assumptions!B43</f>
         <v>7</v>
       </c>
       <c r="C5" s="15" t="n">
-        <f aca="false">Assumptions!$F$37*Assumptions!D41*(1-Assumptions!$B$14)*(1-Assumptions!E41*Assumptions!$B$17)*(1+Assumptions!$B$15*Assumptions!$B$16)</f>
+        <f aca="false">Assumptions!$F$39*Assumptions!D43*(1-Assumptions!$B$16)*(1-Assumptions!E43*Assumptions!$B$19)*(1+Assumptions!$B$17*Assumptions!$B$18)</f>
         <v>2.00334205</v>
       </c>
       <c r="D5" s="15" t="n">
-        <f aca="false">B5*Assumptions!$B$10*Assumptions!$B$11*INDEX(Scenarios!$C$30:$F$30,Assumptions!$B$6)</f>
+        <f aca="false">B5*INDEX(Scenarios!$C$30:$F$30,Assumptions!$B$6)</f>
         <v>1.90604543704274</v>
       </c>
       <c r="E5" s="16" t="n">
@@ -4292,36 +4484,36 @@
         <v>3.90938748704274</v>
       </c>
       <c r="F5" s="21" t="n">
-        <f aca="false">Assumptions!F41*INDEX(Assumptions!$B$73:$D$73,Assumptions!$B$5)/1000*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)</f>
-        <v>0.0108</v>
+        <f aca="false">Assumptions!F43*INDEX(Assumptions!$B$77:$D$77,Assumptions!$B$5)/1000*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)</f>
+        <v>0.00858</v>
       </c>
       <c r="G5" s="22" t="n">
         <f aca="false">IF(F5=0,0,E5/F5)</f>
-        <v>361.980322874328</v>
+        <v>455.639567254399</v>
       </c>
       <c r="H5" s="23" t="n">
-        <f aca="false">Assumptions!G41*INDEX(Assumptions!$B$58:$E$58,Assumptions!$B$6)</f>
-        <v>225</v>
+        <f aca="false">Assumptions!G43*INDEX(Assumptions!$B$60:$E$60,Assumptions!$B$6)</f>
+        <v>180</v>
       </c>
       <c r="I5" s="15" t="n">
         <f aca="false">H5*F5-E5</f>
-        <v>-1.47938748704274</v>
+        <v>-2.36498748704274</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">Assumptions!B42</f>
+        <f aca="false">Assumptions!B44</f>
         <v>3</v>
       </c>
       <c r="C6" s="15" t="n">
-        <f aca="false">Assumptions!$F$37*Assumptions!D42*(1-Assumptions!$B$14)*(1-Assumptions!E42*Assumptions!$B$17)*(1+Assumptions!$B$15*Assumptions!$B$16)</f>
+        <f aca="false">Assumptions!$F$39*Assumptions!D44*(1-Assumptions!$B$16)*(1-Assumptions!E44*Assumptions!$B$19)*(1+Assumptions!$B$17*Assumptions!$B$18)</f>
         <v>1.60267364</v>
       </c>
       <c r="D6" s="15" t="n">
-        <f aca="false">B6*Assumptions!$B$10*Assumptions!$B$11*INDEX(Scenarios!$C$30:$F$30,Assumptions!$B$6)</f>
+        <f aca="false">B6*INDEX(Scenarios!$C$30:$F$30,Assumptions!$B$6)</f>
         <v>0.816876615875461</v>
       </c>
       <c r="E6" s="16" t="n">
@@ -4329,36 +4521,36 @@
         <v>2.41955025587546</v>
       </c>
       <c r="F6" s="21" t="n">
-        <f aca="false">Assumptions!F42*INDEX(Assumptions!$B$73:$D$73,Assumptions!$B$5)/1000*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)</f>
-        <v>0.0054</v>
+        <f aca="false">Assumptions!F44*INDEX(Assumptions!$B$77:$D$77,Assumptions!$B$5)/1000*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)</f>
+        <v>0.00429</v>
       </c>
       <c r="G6" s="22" t="n">
         <f aca="false">IF(F6=0,0,E6/F6)</f>
-        <v>448.064862199159</v>
+        <v>563.997728642299</v>
       </c>
       <c r="H6" s="23" t="n">
-        <f aca="false">Assumptions!G42*INDEX(Assumptions!$B$58:$E$58,Assumptions!$B$6)</f>
-        <v>900</v>
+        <f aca="false">Assumptions!G44*INDEX(Assumptions!$B$60:$E$60,Assumptions!$B$6)</f>
+        <v>750</v>
       </c>
       <c r="I6" s="15" t="n">
         <f aca="false">H6*F6-E6</f>
-        <v>2.44044974412454</v>
+        <v>0.797949744124539</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">Assumptions!B43</f>
+        <f aca="false">Assumptions!B45</f>
         <v>10</v>
       </c>
       <c r="C7" s="15" t="n">
-        <f aca="false">Assumptions!$F$37*Assumptions!D43*(1-Assumptions!$B$14)*(1-Assumptions!E43*Assumptions!$B$17)*(1+Assumptions!$B$15*Assumptions!$B$16)</f>
+        <f aca="false">Assumptions!$F$39*Assumptions!D45*(1-Assumptions!$B$16)*(1-Assumptions!E45*Assumptions!$B$19)*(1+Assumptions!$B$17*Assumptions!$B$18)</f>
         <v>2.604344665</v>
       </c>
       <c r="D7" s="15" t="n">
-        <f aca="false">B7*Assumptions!$B$10*Assumptions!$B$11*INDEX(Scenarios!$C$30:$F$30,Assumptions!$B$6)</f>
+        <f aca="false">B7*INDEX(Scenarios!$C$30:$F$30,Assumptions!$B$6)</f>
         <v>2.7229220529182</v>
       </c>
       <c r="E7" s="16" t="n">
@@ -4366,36 +4558,36 @@
         <v>5.3272667179182</v>
       </c>
       <c r="F7" s="21" t="n">
-        <f aca="false">Assumptions!F43*INDEX(Assumptions!$B$73:$D$73,Assumptions!$B$5)/1000*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)</f>
-        <v>0.0108</v>
+        <f aca="false">Assumptions!F45*INDEX(Assumptions!$B$77:$D$77,Assumptions!$B$5)/1000*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)</f>
+        <v>0.00858</v>
       </c>
       <c r="G7" s="22" t="n">
         <f aca="false">IF(F7=0,0,E7/F7)</f>
-        <v>493.265436844278</v>
+        <v>620.893556866923</v>
       </c>
       <c r="H7" s="23" t="n">
-        <f aca="false">Assumptions!G43*INDEX(Assumptions!$B$58:$E$58,Assumptions!$B$6)</f>
+        <f aca="false">Assumptions!G45*INDEX(Assumptions!$B$60:$E$60,Assumptions!$B$6)</f>
         <v>180</v>
       </c>
       <c r="I7" s="15" t="n">
         <f aca="false">H7*F7-E7</f>
-        <v>-3.3832667179182</v>
+        <v>-3.7828667179182</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">Assumptions!B44</f>
+        <f aca="false">Assumptions!B46</f>
         <v>20</v>
       </c>
       <c r="C8" s="15" t="n">
-        <f aca="false">Assumptions!$F$37*Assumptions!D44*(1-Assumptions!$B$14)*(1-Assumptions!E44*Assumptions!$B$17)*(1+Assumptions!$B$15*Assumptions!$B$16)</f>
+        <f aca="false">Assumptions!$F$39*Assumptions!D46*(1-Assumptions!$B$16)*(1-Assumptions!E46*Assumptions!$B$19)*(1+Assumptions!$B$17*Assumptions!$B$18)</f>
         <v>3.60601569</v>
       </c>
       <c r="D8" s="15" t="n">
-        <f aca="false">B8*Assumptions!$B$10*Assumptions!$B$11*INDEX(Scenarios!$C$30:$F$30,Assumptions!$B$6)</f>
+        <f aca="false">B8*INDEX(Scenarios!$C$30:$F$30,Assumptions!$B$6)</f>
         <v>5.44584410583641</v>
       </c>
       <c r="E8" s="16" t="n">
@@ -4403,36 +4595,36 @@
         <v>9.05185979583641</v>
       </c>
       <c r="F8" s="21" t="n">
-        <f aca="false">Assumptions!F44*INDEX(Assumptions!$B$73:$D$73,Assumptions!$B$5)/1000*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)</f>
-        <v>0.0162</v>
+        <f aca="false">Assumptions!F46*INDEX(Assumptions!$B$77:$D$77,Assumptions!$B$5)/1000*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)</f>
+        <v>0.01287</v>
       </c>
       <c r="G8" s="22" t="n">
         <f aca="false">IF(F8=0,0,E8/F8)</f>
-        <v>558.756777520766</v>
+        <v>703.330209466698</v>
       </c>
       <c r="H8" s="23" t="n">
-        <f aca="false">Assumptions!G44*INDEX(Assumptions!$B$58:$E$58,Assumptions!$B$6)</f>
-        <v>600</v>
+        <f aca="false">Assumptions!G46*INDEX(Assumptions!$B$60:$E$60,Assumptions!$B$6)</f>
+        <v>450</v>
       </c>
       <c r="I8" s="15" t="n">
         <f aca="false">H8*F8-E8</f>
-        <v>0.668140204163594</v>
+        <v>-3.26035979583641</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">Assumptions!B45</f>
+        <f aca="false">Assumptions!B47</f>
         <v>22</v>
       </c>
       <c r="C9" s="15" t="n">
-        <f aca="false">Assumptions!$F$37*Assumptions!D45*(1-Assumptions!$B$14)*(1-Assumptions!E45*Assumptions!$B$17)*(1+Assumptions!$B$15*Assumptions!$B$16)</f>
+        <f aca="false">Assumptions!$F$39*Assumptions!D47*(1-Assumptions!$B$16)*(1-Assumptions!E47*Assumptions!$B$19)*(1+Assumptions!$B$17*Assumptions!$B$18)</f>
         <v>2.203676255</v>
       </c>
       <c r="D9" s="15" t="n">
-        <f aca="false">B9*Assumptions!$B$10*Assumptions!$B$11*INDEX(Scenarios!$C$30:$F$30,Assumptions!$B$6)</f>
+        <f aca="false">B9*INDEX(Scenarios!$C$30:$F$30,Assumptions!$B$6)</f>
         <v>5.99042851642005</v>
       </c>
       <c r="E9" s="16" t="n">
@@ -4440,36 +4632,36 @@
         <v>8.19410477142005</v>
       </c>
       <c r="F9" s="21" t="n">
-        <f aca="false">Assumptions!F45*INDEX(Assumptions!$B$73:$D$73,Assumptions!$B$5)/1000*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)</f>
-        <v>0.0162</v>
+        <f aca="false">Assumptions!F47*INDEX(Assumptions!$B$77:$D$77,Assumptions!$B$5)/1000*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)</f>
+        <v>0.01287</v>
       </c>
       <c r="G9" s="22" t="n">
         <f aca="false">IF(F9=0,0,E9/F9)</f>
-        <v>505.80893650741</v>
+        <v>636.682577421915</v>
       </c>
       <c r="H9" s="23" t="n">
-        <f aca="false">Assumptions!G45*INDEX(Assumptions!$B$58:$E$58,Assumptions!$B$6)</f>
-        <v>1050</v>
+        <f aca="false">Assumptions!G47*INDEX(Assumptions!$B$60:$E$60,Assumptions!$B$6)</f>
+        <v>600</v>
       </c>
       <c r="I9" s="15" t="n">
         <f aca="false">H9*F9-E9</f>
-        <v>8.81589522857995</v>
+        <v>-0.472104771420046</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">Assumptions!B46</f>
+        <f aca="false">Assumptions!B48</f>
         <v>18</v>
       </c>
       <c r="C10" s="15" t="n">
-        <f aca="false">Assumptions!$F$37*Assumptions!D46*(1-Assumptions!$B$14)*(1-Assumptions!E46*Assumptions!$B$17)*(1+Assumptions!$B$15*Assumptions!$B$16)</f>
+        <f aca="false">Assumptions!$F$39*Assumptions!D48*(1-Assumptions!$B$16)*(1-Assumptions!E48*Assumptions!$B$19)*(1+Assumptions!$B$17*Assumptions!$B$18)</f>
         <v>1.803007845</v>
       </c>
       <c r="D10" s="15" t="n">
-        <f aca="false">B10*Assumptions!$B$10*Assumptions!$B$11*INDEX(Scenarios!$C$30:$F$30,Assumptions!$B$6)</f>
+        <f aca="false">B10*INDEX(Scenarios!$C$30:$F$30,Assumptions!$B$6)</f>
         <v>4.90125969525276</v>
       </c>
       <c r="E10" s="16" t="n">
@@ -4477,36 +4669,36 @@
         <v>6.70426754025276</v>
       </c>
       <c r="F10" s="21" t="n">
-        <f aca="false">Assumptions!F46*INDEX(Assumptions!$B$73:$D$73,Assumptions!$B$5)/1000*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)</f>
-        <v>0.0162</v>
+        <f aca="false">Assumptions!F48*INDEX(Assumptions!$B$77:$D$77,Assumptions!$B$5)/1000*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)</f>
+        <v>0.01287</v>
       </c>
       <c r="G10" s="22" t="n">
         <f aca="false">IF(F10=0,0,E10/F10)</f>
-        <v>413.843675324245</v>
+        <v>520.922108799749</v>
       </c>
       <c r="H10" s="23" t="n">
-        <f aca="false">Assumptions!G46*INDEX(Assumptions!$B$58:$E$58,Assumptions!$B$6)</f>
-        <v>750</v>
+        <f aca="false">Assumptions!G48*INDEX(Assumptions!$B$60:$E$60,Assumptions!$B$6)</f>
+        <v>600</v>
       </c>
       <c r="I10" s="15" t="n">
         <f aca="false">H10*F10-E10</f>
-        <v>5.44573245974723</v>
+        <v>1.01773245974724</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">Assumptions!B47</f>
+        <f aca="false">Assumptions!B49</f>
         <v>5</v>
       </c>
       <c r="C11" s="15" t="n">
-        <f aca="false">Assumptions!$F$37*Assumptions!D47*(1-Assumptions!$B$14)*(1-Assumptions!E47*Assumptions!$B$17)*(1+Assumptions!$B$15*Assumptions!$B$16)</f>
+        <f aca="false">Assumptions!$F$39*Assumptions!D49*(1-Assumptions!$B$16)*(1-Assumptions!E49*Assumptions!$B$19)*(1+Assumptions!$B$17*Assumptions!$B$18)</f>
         <v>1.20200523</v>
       </c>
       <c r="D11" s="15" t="n">
-        <f aca="false">B11*Assumptions!$B$10*Assumptions!$B$11*INDEX(Scenarios!$C$30:$F$30,Assumptions!$B$6)</f>
+        <f aca="false">B11*INDEX(Scenarios!$C$30:$F$30,Assumptions!$B$6)</f>
         <v>1.3614610264591</v>
       </c>
       <c r="E11" s="16" t="n">
@@ -4514,20 +4706,20 @@
         <v>2.5634662564591</v>
       </c>
       <c r="F11" s="21" t="n">
-        <f aca="false">Assumptions!F47*INDEX(Assumptions!$B$73:$D$73,Assumptions!$B$5)/1000*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)</f>
-        <v>0.0054</v>
+        <f aca="false">Assumptions!F49*INDEX(Assumptions!$B$77:$D$77,Assumptions!$B$5)/1000*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)</f>
+        <v>0.00429</v>
       </c>
       <c r="G11" s="22" t="n">
         <f aca="false">IF(F11=0,0,E11/F11)</f>
-        <v>474.715973418352</v>
+        <v>597.544581925199</v>
       </c>
       <c r="H11" s="23" t="n">
-        <f aca="false">Assumptions!G47*INDEX(Assumptions!$B$58:$E$58,Assumptions!$B$6)</f>
+        <f aca="false">Assumptions!G49*INDEX(Assumptions!$B$60:$E$60,Assumptions!$B$6)</f>
         <v>90</v>
       </c>
       <c r="I11" s="15" t="n">
         <f aca="false">H11*F11-E11</f>
-        <v>-2.0774662564591</v>
+        <v>-2.1773662564591</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4543,7 +4735,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -4581,7 +4773,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4591,7 +4783,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4601,7 +4793,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5" t="s">
@@ -4629,161 +4821,161 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="23" t="n">
-        <f aca="false">Assumptions!B51</f>
+        <f aca="false">Assumptions!B53</f>
         <v>2</v>
       </c>
       <c r="D5" s="23" t="n">
-        <f aca="false">Assumptions!C51</f>
+        <f aca="false">Assumptions!C53</f>
         <v>6</v>
       </c>
       <c r="E5" s="23" t="n">
-        <f aca="false">Assumptions!D51</f>
+        <f aca="false">Assumptions!D53</f>
         <v>25</v>
       </c>
       <c r="F5" s="23" t="n">
-        <f aca="false">Assumptions!E51</f>
+        <f aca="false">Assumptions!E53</f>
         <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="23" t="n">
-        <f aca="false">Assumptions!B52</f>
+        <f aca="false">Assumptions!B54</f>
         <v>1</v>
       </c>
       <c r="D6" s="23" t="n">
-        <f aca="false">Assumptions!C52</f>
+        <f aca="false">Assumptions!C54</f>
         <v>2</v>
       </c>
       <c r="E6" s="23" t="n">
-        <f aca="false">Assumptions!D52</f>
+        <f aca="false">Assumptions!D54</f>
         <v>3</v>
       </c>
       <c r="F6" s="23" t="n">
-        <f aca="false">Assumptions!E52</f>
+        <f aca="false">Assumptions!E54</f>
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="23" t="n">
-        <f aca="false">Assumptions!B53</f>
+        <f aca="false">Assumptions!B55</f>
         <v>1</v>
       </c>
       <c r="D7" s="23" t="n">
-        <f aca="false">Assumptions!C53</f>
+        <f aca="false">Assumptions!C55</f>
         <v>3</v>
       </c>
       <c r="E7" s="23" t="n">
-        <f aca="false">Assumptions!D53</f>
+        <f aca="false">Assumptions!D55</f>
         <v>10</v>
       </c>
       <c r="F7" s="23" t="n">
-        <f aca="false">Assumptions!E53</f>
+        <f aca="false">Assumptions!E55</f>
         <v>30</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="23" t="n">
-        <f aca="false">Assumptions!B54</f>
+        <f aca="false">Assumptions!B56</f>
         <v>1</v>
       </c>
       <c r="D8" s="23" t="n">
-        <f aca="false">Assumptions!C54</f>
+        <f aca="false">Assumptions!C56</f>
         <v>1</v>
       </c>
       <c r="E8" s="23" t="n">
-        <f aca="false">Assumptions!D54</f>
+        <f aca="false">Assumptions!D56</f>
         <v>2</v>
       </c>
       <c r="F8" s="23" t="n">
-        <f aca="false">Assumptions!E54</f>
+        <f aca="false">Assumptions!E56</f>
         <v>4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="23" t="n">
-        <f aca="false">Assumptions!B55</f>
+        <f aca="false">Assumptions!B57</f>
         <v>1</v>
       </c>
       <c r="D9" s="23" t="n">
-        <f aca="false">Assumptions!C55</f>
+        <f aca="false">Assumptions!C57</f>
         <v>1</v>
       </c>
       <c r="E9" s="23" t="n">
-        <f aca="false">Assumptions!D55</f>
+        <f aca="false">Assumptions!D57</f>
         <v>2</v>
       </c>
       <c r="F9" s="23" t="n">
-        <f aca="false">Assumptions!E55</f>
+        <f aca="false">Assumptions!E57</f>
         <v>4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="23" t="n">
-        <f aca="false">Assumptions!B56</f>
+        <f aca="false">Assumptions!B58</f>
         <v>1</v>
       </c>
       <c r="D10" s="23" t="n">
-        <f aca="false">Assumptions!C56</f>
+        <f aca="false">Assumptions!C58</f>
         <v>4</v>
       </c>
       <c r="E10" s="23" t="n">
-        <f aca="false">Assumptions!D56</f>
+        <f aca="false">Assumptions!D58</f>
         <v>15</v>
       </c>
       <c r="F10" s="23" t="n">
-        <f aca="false">Assumptions!E56</f>
+        <f aca="false">Assumptions!E58</f>
         <v>50</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="23" t="n">
-        <f aca="false">Assumptions!B57</f>
+        <f aca="false">Assumptions!B59</f>
         <v>0</v>
       </c>
       <c r="D11" s="23" t="n">
-        <f aca="false">Assumptions!C57</f>
+        <f aca="false">Assumptions!C59</f>
         <v>10</v>
       </c>
       <c r="E11" s="23" t="n">
-        <f aca="false">Assumptions!D57</f>
+        <f aca="false">Assumptions!D59</f>
         <v>100</v>
       </c>
       <c r="F11" s="23" t="n">
-        <f aca="false">Assumptions!E57</f>
+        <f aca="false">Assumptions!E59</f>
         <v>500</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="22" t="n">
@@ -4805,7 +4997,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -4815,161 +5007,161 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="23" t="n">
-        <f aca="false">C5*Assumptions!$C$41</f>
+        <f aca="false">C5*Assumptions!$C$43</f>
         <v>43.4</v>
       </c>
       <c r="D14" s="23" t="n">
-        <f aca="false">D5*Assumptions!$C$41</f>
+        <f aca="false">D5*Assumptions!$C$43</f>
         <v>130.2</v>
       </c>
       <c r="E14" s="23" t="n">
-        <f aca="false">E5*Assumptions!$C$41</f>
+        <f aca="false">E5*Assumptions!$C$43</f>
         <v>542.5</v>
       </c>
       <c r="F14" s="23" t="n">
-        <f aca="false">F5*Assumptions!$C$41</f>
+        <f aca="false">F5*Assumptions!$C$43</f>
         <v>2170</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="23" t="n">
-        <f aca="false">C6*Assumptions!$C$42</f>
+        <f aca="false">C6*Assumptions!$C$44</f>
         <v>30</v>
       </c>
       <c r="D15" s="23" t="n">
-        <f aca="false">D6*Assumptions!$C$42</f>
+        <f aca="false">D6*Assumptions!$C$44</f>
         <v>60</v>
       </c>
       <c r="E15" s="23" t="n">
-        <f aca="false">E6*Assumptions!$C$42</f>
+        <f aca="false">E6*Assumptions!$C$44</f>
         <v>90</v>
       </c>
       <c r="F15" s="23" t="n">
-        <f aca="false">F6*Assumptions!$C$42</f>
+        <f aca="false">F6*Assumptions!$C$44</f>
         <v>150</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="23" t="n">
-        <f aca="false">C7*Assumptions!$C$43</f>
+        <f aca="false">C7*Assumptions!$C$45</f>
         <v>21.7</v>
       </c>
       <c r="D16" s="23" t="n">
-        <f aca="false">D7*Assumptions!$C$43</f>
+        <f aca="false">D7*Assumptions!$C$45</f>
         <v>65.1</v>
       </c>
       <c r="E16" s="23" t="n">
-        <f aca="false">E7*Assumptions!$C$43</f>
+        <f aca="false">E7*Assumptions!$C$45</f>
         <v>217</v>
       </c>
       <c r="F16" s="23" t="n">
-        <f aca="false">F7*Assumptions!$C$43</f>
+        <f aca="false">F7*Assumptions!$C$45</f>
         <v>651</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="23" t="n">
-        <f aca="false">C8*Assumptions!$C$44</f>
+        <f aca="false">C8*Assumptions!$C$46</f>
         <v>8.3</v>
       </c>
       <c r="D17" s="23" t="n">
-        <f aca="false">D8*Assumptions!$C$44</f>
+        <f aca="false">D8*Assumptions!$C$46</f>
         <v>8.3</v>
       </c>
       <c r="E17" s="23" t="n">
-        <f aca="false">E8*Assumptions!$C$44</f>
+        <f aca="false">E8*Assumptions!$C$46</f>
         <v>16.6</v>
       </c>
       <c r="F17" s="23" t="n">
-        <f aca="false">F8*Assumptions!$C$44</f>
+        <f aca="false">F8*Assumptions!$C$46</f>
         <v>33.2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="23" t="n">
-        <f aca="false">C9*Assumptions!$C$45</f>
+        <f aca="false">C9*Assumptions!$C$47</f>
         <v>8.7</v>
       </c>
       <c r="D18" s="23" t="n">
-        <f aca="false">D9*Assumptions!$C$45</f>
+        <f aca="false">D9*Assumptions!$C$47</f>
         <v>8.7</v>
       </c>
       <c r="E18" s="23" t="n">
-        <f aca="false">E9*Assumptions!$C$45</f>
+        <f aca="false">E9*Assumptions!$C$47</f>
         <v>17.4</v>
       </c>
       <c r="F18" s="23" t="n">
-        <f aca="false">F9*Assumptions!$C$45</f>
+        <f aca="false">F9*Assumptions!$C$47</f>
         <v>34.8</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="24" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="23" t="n">
-        <f aca="false">C10*Assumptions!$C$46</f>
+        <f aca="false">C10*Assumptions!$C$48</f>
         <v>13</v>
       </c>
       <c r="D19" s="23" t="n">
-        <f aca="false">D10*Assumptions!$C$46</f>
+        <f aca="false">D10*Assumptions!$C$48</f>
         <v>52</v>
       </c>
       <c r="E19" s="23" t="n">
-        <f aca="false">E10*Assumptions!$C$46</f>
+        <f aca="false">E10*Assumptions!$C$48</f>
         <v>195</v>
       </c>
       <c r="F19" s="23" t="n">
-        <f aca="false">F10*Assumptions!$C$46</f>
+        <f aca="false">F10*Assumptions!$C$48</f>
         <v>650</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="23" t="n">
-        <f aca="false">C11*Assumptions!$C$47</f>
+        <f aca="false">C11*Assumptions!$C$49</f>
         <v>0</v>
       </c>
       <c r="D20" s="23" t="n">
-        <f aca="false">D11*Assumptions!$C$47</f>
+        <f aca="false">D11*Assumptions!$C$49</f>
         <v>120</v>
       </c>
       <c r="E20" s="23" t="n">
-        <f aca="false">E11*Assumptions!$C$47</f>
+        <f aca="false">E11*Assumptions!$C$49</f>
         <v>1200</v>
       </c>
       <c r="F20" s="23" t="n">
-        <f aca="false">F11*Assumptions!$C$47</f>
+        <f aca="false">F11*Assumptions!$C$49</f>
         <v>6000</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="22" t="n">
@@ -4991,46 +5183,46 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="24" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="23" t="n">
-        <f aca="false">C14*Assumptions!$B$41+C15*Assumptions!$B$42+C16*Assumptions!$B$43+C17*Assumptions!$B$44+C18*Assumptions!$B$45+C19*Assumptions!$B$46+C20*Assumptions!$B$47</f>
+        <f aca="false">C14*Assumptions!$B$43+C15*Assumptions!$B$44+C16*Assumptions!$B$45+C17*Assumptions!$B$46+C18*Assumptions!$B$47+C19*Assumptions!$B$48+C20*Assumptions!$B$49</f>
         <v>1202.2</v>
       </c>
       <c r="D22" s="23" t="n">
-        <f aca="false">D14*Assumptions!$B$41+D15*Assumptions!$B$42+D16*Assumptions!$B$43+D17*Assumptions!$B$44+D18*Assumptions!$B$45+D19*Assumptions!$B$46+D20*Assumptions!$B$47</f>
+        <f aca="false">D14*Assumptions!$B$43+D15*Assumptions!$B$44+D16*Assumptions!$B$45+D17*Assumptions!$B$46+D18*Assumptions!$B$47+D19*Assumptions!$B$48+D20*Assumptions!$B$49</f>
         <v>3635.8</v>
       </c>
       <c r="E22" s="23" t="n">
-        <f aca="false">E14*Assumptions!$B$41+E15*Assumptions!$B$42+E16*Assumptions!$B$43+E17*Assumptions!$B$44+E18*Assumptions!$B$45+E19*Assumptions!$B$46+E20*Assumptions!$B$47</f>
+        <f aca="false">E14*Assumptions!$B$43+E15*Assumptions!$B$44+E16*Assumptions!$B$45+E17*Assumptions!$B$46+E18*Assumptions!$B$47+E19*Assumptions!$B$48+E20*Assumptions!$B$49</f>
         <v>16462.3</v>
       </c>
       <c r="F22" s="23" t="n">
-        <f aca="false">F14*Assumptions!$B$41+F15*Assumptions!$B$42+F16*Assumptions!$B$43+F17*Assumptions!$B$44+F18*Assumptions!$B$45+F19*Assumptions!$B$46+F20*Assumptions!$B$47</f>
+        <f aca="false">F14*Assumptions!$B$43+F15*Assumptions!$B$44+F16*Assumptions!$B$45+F17*Assumptions!$B$46+F18*Assumptions!$B$47+F19*Assumptions!$B$48+F20*Assumptions!$B$49</f>
         <v>65279.6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="24" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="23" t="n">
-        <f aca="false">C22*Assumptions!$B$10*Assumptions!$B$11</f>
-        <v>1202200</v>
+        <f aca="false">MAX(0,C22*(1-Assumptions!B$72)*Assumptions!$B$10*Assumptions!$B$11*Assumptions!$B$12-Assumptions!B$73)</f>
+        <v>1502750</v>
       </c>
       <c r="D23" s="23" t="n">
-        <f aca="false">D22*Assumptions!$B$10*Assumptions!$B$11</f>
-        <v>3635800</v>
+        <f aca="false">MAX(0,D22*(1-Assumptions!C$72)*Assumptions!$B$10*Assumptions!$B$11*Assumptions!$B$12-Assumptions!C$73)</f>
+        <v>4544750</v>
       </c>
       <c r="E23" s="23" t="n">
-        <f aca="false">E22*Assumptions!$B$10*Assumptions!$B$11</f>
-        <v>16462300</v>
+        <f aca="false">MAX(0,E22*(1-Assumptions!D$72)*Assumptions!$B$10*Assumptions!$B$11*Assumptions!$B$12-Assumptions!D$73)</f>
+        <v>20577875</v>
       </c>
       <c r="F23" s="23" t="n">
-        <f aca="false">F22*Assumptions!$B$10*Assumptions!$B$11</f>
-        <v>65279600</v>
+        <f aca="false">MAX(0,F22*(1-Assumptions!E$72)*Assumptions!$B$10*Assumptions!$B$11*Assumptions!$B$12-Assumptions!E$73)</f>
+        <v>81599500</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5051,56 +5243,56 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="24" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="25" t="n">
-        <f aca="false">INDEX(Assumptions!$B$62:$B$66,MATCH(Assumptions!B$68,Assumptions!$A$62:$A$66,0))</f>
-        <v>99</v>
+        <f aca="false">INDEX(Assumptions!$B$64:$B$68,MATCH(Assumptions!B$70,Assumptions!$A$64:$A$68,0))</f>
+        <v>299</v>
       </c>
       <c r="D26" s="25" t="n">
-        <f aca="false">INDEX(Assumptions!$B$62:$B$66,MATCH(Assumptions!C$68,Assumptions!$A$62:$A$66,0))</f>
+        <f aca="false">INDEX(Assumptions!$B$64:$B$68,MATCH(Assumptions!C$70,Assumptions!$A$64:$A$68,0))</f>
         <v>990</v>
       </c>
       <c r="E26" s="25" t="n">
-        <f aca="false">INDEX(Assumptions!$B$62:$B$66,MATCH(Assumptions!D$68,Assumptions!$A$62:$A$66,0))</f>
+        <f aca="false">INDEX(Assumptions!$B$64:$B$68,MATCH(Assumptions!D$70,Assumptions!$A$64:$A$68,0))</f>
         <v>3000</v>
       </c>
       <c r="F26" s="25" t="n">
-        <f aca="false">INDEX(Assumptions!$B$62:$B$66,MATCH(Assumptions!E$68,Assumptions!$A$62:$A$66,0))</f>
+        <f aca="false">INDEX(Assumptions!$B$64:$B$68,MATCH(Assumptions!E$70,Assumptions!$A$64:$A$68,0))</f>
         <v>3000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="24" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="23" t="n">
-        <f aca="false">INDEX(Assumptions!$C$62:$C$66,MATCH(Assumptions!B$68,Assumptions!$A$62:$A$66,0))</f>
-        <v>600000</v>
+        <f aca="false">INDEX(Assumptions!$C$64:$C$68,MATCH(Assumptions!B$70,Assumptions!$A$64:$A$68,0))</f>
+        <v>1800000</v>
       </c>
       <c r="D27" s="23" t="n">
-        <f aca="false">INDEX(Assumptions!$C$62:$C$66,MATCH(Assumptions!C$68,Assumptions!$A$62:$A$66,0))</f>
+        <f aca="false">INDEX(Assumptions!$C$64:$C$68,MATCH(Assumptions!C$70,Assumptions!$A$64:$A$68,0))</f>
         <v>6000000</v>
       </c>
       <c r="E27" s="23" t="n">
-        <f aca="false">INDEX(Assumptions!$C$62:$C$66,MATCH(Assumptions!D$68,Assumptions!$A$62:$A$66,0))</f>
+        <f aca="false">INDEX(Assumptions!$C$64:$C$68,MATCH(Assumptions!D$70,Assumptions!$A$64:$A$68,0))</f>
         <v>30000000</v>
       </c>
       <c r="F27" s="23" t="n">
-        <f aca="false">INDEX(Assumptions!$C$62:$C$66,MATCH(Assumptions!E$68,Assumptions!$A$62:$A$66,0))</f>
+        <f aca="false">INDEX(Assumptions!$C$64:$C$68,MATCH(Assumptions!E$70,Assumptions!$A$64:$A$68,0))</f>
         <v>30000000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="24" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="23" t="n">
         <f aca="false">MAX(0,C23-C27)</f>
-        <v>602200</v>
+        <v>0</v>
       </c>
       <c r="D28" s="23" t="n">
         <f aca="false">MAX(0,D23-D27)</f>
@@ -5112,56 +5304,56 @@
       </c>
       <c r="F28" s="23" t="n">
         <f aca="false">MAX(0,F23-F27)</f>
-        <v>35279600</v>
+        <v>51599500</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="26" t="n">
-        <f aca="false">C26+C28/1000*Assumptions!B$69</f>
-        <v>189.33</v>
+        <f aca="false">C26+C28/1000*Assumptions!B$71+C22*Assumptions!B$72*Assumptions!$B$13</f>
+        <v>299</v>
       </c>
       <c r="D29" s="26" t="n">
-        <f aca="false">D26+D28/1000*Assumptions!C$69</f>
+        <f aca="false">D26+D28/1000*Assumptions!C$71+D22*Assumptions!C$72*Assumptions!$B$13</f>
         <v>990</v>
       </c>
       <c r="E29" s="26" t="n">
-        <f aca="false">E26+E28/1000*Assumptions!D$69</f>
+        <f aca="false">E26+E28/1000*Assumptions!D$71+E22*Assumptions!D$72*Assumptions!$B$13</f>
         <v>3000</v>
       </c>
       <c r="F29" s="26" t="n">
-        <f aca="false">F26+F28/1000*Assumptions!E$69</f>
-        <v>5116.776</v>
+        <f aca="false">F26+F28/1000*Assumptions!E$71+F22*Assumptions!E$72*Assumptions!$B$13</f>
+        <v>8159.95</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="24" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B30" s="2"/>
-      <c r="C30" s="27" t="n">
-        <f aca="false">IF(C23=0,0,C29/C23)</f>
-        <v>0.000157486275162203</v>
-      </c>
-      <c r="D30" s="27" t="n">
-        <f aca="false">IF(D23=0,0,D29/D23)</f>
-        <v>0.00027229220529182</v>
-      </c>
-      <c r="E30" s="27" t="n">
-        <f aca="false">IF(E23=0,0,E29/E23)</f>
-        <v>0.000182234560176889</v>
-      </c>
-      <c r="F30" s="27" t="n">
-        <f aca="false">IF(F23=0,0,F29/F23)</f>
-        <v>7.83824655788332E-005</v>
+      <c r="C30" s="21" t="n">
+        <f aca="false">IF(C22=0,0,C29/C22)</f>
+        <v>0.248710697055398</v>
+      </c>
+      <c r="D30" s="21" t="n">
+        <f aca="false">IF(D22=0,0,D29/D22)</f>
+        <v>0.27229220529182</v>
+      </c>
+      <c r="E30" s="21" t="n">
+        <f aca="false">IF(E22=0,0,E29/E22)</f>
+        <v>0.182234560176889</v>
+      </c>
+      <c r="F30" s="21" t="n">
+        <f aca="false">IF(F22=0,0,F29/F22)</f>
+        <v>0.125</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="26" t="n">
@@ -5183,68 +5375,68 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" s="7" t="n">
-        <f aca="false">'Cost Lines'!J18</f>
-        <v>199.99</v>
+        <f aca="false">'Cost Lines'!J20</f>
+        <v>868.66</v>
       </c>
       <c r="D32" s="7" t="n">
-        <f aca="false">'Cost Lines'!K18</f>
-        <v>248.99</v>
+        <f aca="false">'Cost Lines'!K20</f>
+        <v>1022.67</v>
       </c>
       <c r="E32" s="7" t="n">
-        <f aca="false">'Cost Lines'!L18</f>
-        <v>405</v>
+        <f aca="false">'Cost Lines'!L20</f>
+        <v>1919.67</v>
       </c>
       <c r="F32" s="7" t="n">
-        <f aca="false">'Cost Lines'!M18</f>
-        <v>792</v>
+        <f aca="false">'Cost Lines'!M20</f>
+        <v>4699.67</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="28" t="s">
-        <v>189</v>
+      <c r="A33" s="27" t="s">
+        <v>197</v>
       </c>
       <c r="B33" s="2"/>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="28" t="n">
         <f aca="false">C29+C31+C32</f>
-        <v>653.400549031</v>
-      </c>
-      <c r="D33" s="29" t="n">
+        <v>1431.740549031</v>
+      </c>
+      <c r="D33" s="28" t="n">
         <f aca="false">D29+D31+D32</f>
-        <v>2052.627340187</v>
-      </c>
-      <c r="E33" s="29" t="n">
+        <v>2826.307340187</v>
+      </c>
+      <c r="E33" s="28" t="n">
         <f aca="false">E29+E31+E32</f>
-        <v>7093.393115096</v>
-      </c>
-      <c r="F33" s="29" t="n">
+        <v>8608.063115096</v>
+      </c>
+      <c r="F33" s="28" t="n">
         <f aca="false">F29+F31+F32</f>
-        <v>20772.251805247</v>
+        <v>27723.095805247</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="24" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="15" t="n">
         <f aca="false">IF(C21=0,0,C33/C21)</f>
-        <v>5.22302597147082</v>
+        <v>11.4447685773861</v>
       </c>
       <c r="D34" s="15" t="n">
         <f aca="false">IF(D21=0,0,D33/D21)</f>
-        <v>4.61991298714157</v>
+        <v>6.36125892457124</v>
       </c>
       <c r="E34" s="15" t="n">
         <f aca="false">IF(E21=0,0,E33/E21)</f>
-        <v>3.11318547952425</v>
+        <v>3.77795177313847</v>
       </c>
       <c r="F34" s="15" t="n">
         <f aca="false">IF(F21=0,0,F33/F21)</f>
-        <v>2.14390048562772</v>
+        <v>2.8612958824695</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5257,7 +5449,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -5271,306 +5463,306 @@
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="23" t="n">
-        <f aca="false">(C14*Assumptions!$G$41+C15*Assumptions!$G$42+C16*Assumptions!$G$43+C17*Assumptions!$G$44+C18*Assumptions!$G$45+C19*Assumptions!$G$46+C20*Assumptions!$G$47)*Assumptions!B$58</f>
-        <v>43024</v>
+        <f aca="false">(C14*Assumptions!$G$43+C15*Assumptions!$G$44+C16*Assumptions!$G$45+C17*Assumptions!$G$46+C18*Assumptions!$G$47+C19*Assumptions!$G$48+C20*Assumptions!$G$49)*Assumptions!B$60</f>
+        <v>33982</v>
       </c>
       <c r="D37" s="23" t="n">
-        <f aca="false">(D14*Assumptions!$G$41+D15*Assumptions!$G$42+D16*Assumptions!$G$43+D17*Assumptions!$G$44+D18*Assumptions!$G$45+D19*Assumptions!$G$46+D20*Assumptions!$G$47)*Assumptions!C$58</f>
-        <v>158928</v>
+        <f aca="false">(D14*Assumptions!$G$43+D15*Assumptions!$G$44+D16*Assumptions!$G$45+D17*Assumptions!$G$46+D18*Assumptions!$G$47+D19*Assumptions!$G$48+D20*Assumptions!$G$49)*Assumptions!C$60</f>
+        <v>131109</v>
       </c>
       <c r="E37" s="23" t="n">
-        <f aca="false">(E14*Assumptions!$G$41+E15*Assumptions!$G$42+E16*Assumptions!$G$43+E17*Assumptions!$G$44+E18*Assumptions!$G$45+E19*Assumptions!$G$46+E20*Assumptions!$G$47)*Assumptions!D$58</f>
-        <v>874337.5</v>
+        <f aca="false">(E14*Assumptions!$G$43+E15*Assumptions!$G$44+E16*Assumptions!$G$45+E17*Assumptions!$G$46+E18*Assumptions!$G$47+E19*Assumptions!$G$48+E20*Assumptions!$G$49)*Assumptions!D$60</f>
+        <v>670680</v>
       </c>
       <c r="F37" s="23" t="n">
-        <f aca="false">(F14*Assumptions!$G$41+F15*Assumptions!$G$42+F16*Assumptions!$G$43+F17*Assumptions!$G$44+F18*Assumptions!$G$45+F19*Assumptions!$G$46+F20*Assumptions!$G$47)*Assumptions!E$58</f>
-        <v>4256910</v>
+        <f aca="false">(F14*Assumptions!$G$43+F15*Assumptions!$G$44+F16*Assumptions!$G$45+F17*Assumptions!$G$46+F18*Assumptions!$G$47+F19*Assumptions!$G$48+F20*Assumptions!$G$49)*Assumptions!E$60</f>
+        <v>3172200</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="24" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" s="25" t="n">
-        <f aca="false">(C14*Assumptions!$G$41*Assumptions!$F$41+C15*Assumptions!$G$42*Assumptions!$F$42+C16*Assumptions!$G$43*Assumptions!$F$43+C17*Assumptions!$G$44*Assumptions!$F$44+C18*Assumptions!$G$45*Assumptions!$F$45+C19*Assumptions!$G$46*Assumptions!$F$46+C20*Assumptions!$G$47*Assumptions!$F$47)*Assumptions!B$58/1000*INDEX(Assumptions!$B$73:$D$73,Assumptions!$B$5)*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)</f>
-        <v>453.3732</v>
+        <f aca="false">(C14*Assumptions!$G$43*Assumptions!$F$43+C15*Assumptions!$G$44*Assumptions!$F$44+C16*Assumptions!$G$45*Assumptions!$F$45+C17*Assumptions!$G$46*Assumptions!$F$46+C18*Assumptions!$G$47*Assumptions!$F$47+C19*Assumptions!$G$48*Assumptions!$F$48+C20*Assumptions!$G$49*Assumptions!$F$49)*Assumptions!B$60/1000*INDEX(Assumptions!$B$77:$D$77,Assumptions!$B$5)*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)</f>
+        <v>275.13486</v>
       </c>
       <c r="D38" s="25" t="n">
-        <f aca="false">(D14*Assumptions!$G$41*Assumptions!$F$41+D15*Assumptions!$G$42*Assumptions!$F$42+D16*Assumptions!$G$43*Assumptions!$F$43+D17*Assumptions!$G$44*Assumptions!$F$44+D18*Assumptions!$G$45*Assumptions!$F$45+D19*Assumptions!$G$46*Assumptions!$F$46+D20*Assumptions!$G$47*Assumptions!$F$47)*Assumptions!C$58/1000*INDEX(Assumptions!$B$73:$D$73,Assumptions!$B$5)*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)</f>
-        <v>1653.3234</v>
+        <f aca="false">(D14*Assumptions!$G$43*Assumptions!$F$43+D15*Assumptions!$G$44*Assumptions!$F$44+D16*Assumptions!$G$45*Assumptions!$F$45+D17*Assumptions!$G$46*Assumptions!$F$46+D18*Assumptions!$G$47*Assumptions!$F$47+D19*Assumptions!$G$48*Assumptions!$F$48+D20*Assumptions!$G$49*Assumptions!$F$49)*Assumptions!C$60/1000*INDEX(Assumptions!$B$77:$D$77,Assumptions!$B$5)*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)</f>
+        <v>1057.79817</v>
       </c>
       <c r="E38" s="25" t="n">
-        <f aca="false">(E14*Assumptions!$G$41*Assumptions!$F$41+E15*Assumptions!$G$42*Assumptions!$F$42+E16*Assumptions!$G$43*Assumptions!$F$43+E17*Assumptions!$G$44*Assumptions!$F$44+E18*Assumptions!$G$45*Assumptions!$F$45+E19*Assumptions!$G$46*Assumptions!$F$46+E20*Assumptions!$G$47*Assumptions!$F$47)*Assumptions!D$58/1000*INDEX(Assumptions!$B$73:$D$73,Assumptions!$B$5)*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)</f>
-        <v>9312.165</v>
+        <f aca="false">(E14*Assumptions!$G$43*Assumptions!$F$43+E15*Assumptions!$G$44*Assumptions!$F$44+E16*Assumptions!$G$45*Assumptions!$F$45+E17*Assumptions!$G$46*Assumptions!$F$46+E18*Assumptions!$G$47*Assumptions!$F$47+E19*Assumptions!$G$48*Assumptions!$F$48+E20*Assumptions!$G$49*Assumptions!$F$49)*Assumptions!D$60/1000*INDEX(Assumptions!$B$77:$D$77,Assumptions!$B$5)*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)</f>
+        <v>5493.23775</v>
       </c>
       <c r="F38" s="25" t="n">
-        <f aca="false">(F14*Assumptions!$G$41*Assumptions!$F$41+F15*Assumptions!$G$42*Assumptions!$F$42+F16*Assumptions!$G$43*Assumptions!$F$43+F17*Assumptions!$G$44*Assumptions!$F$44+F18*Assumptions!$G$45*Assumptions!$F$45+F19*Assumptions!$G$46*Assumptions!$F$46+F20*Assumptions!$G$47*Assumptions!$F$47)*Assumptions!E$58/1000*INDEX(Assumptions!$B$73:$D$73,Assumptions!$B$5)*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)</f>
-        <v>44323.524</v>
+        <f aca="false">(F14*Assumptions!$G$43*Assumptions!$F$43+F15*Assumptions!$G$44*Assumptions!$F$44+F16*Assumptions!$G$45*Assumptions!$F$45+F17*Assumptions!$G$46*Assumptions!$F$46+F18*Assumptions!$G$47*Assumptions!$F$47+F19*Assumptions!$G$48*Assumptions!$F$48+F20*Assumptions!$G$49*Assumptions!$F$49)*Assumptions!E$60/1000*INDEX(Assumptions!$B$77:$D$77,Assumptions!$B$5)*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)</f>
+        <v>25272.5616</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="24" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="25" t="n">
-        <f aca="false">(C5+C7)*Assumptions!B$85*INDEX(Assumptions!$B$76:$D$76,Assumptions!$B$5)</f>
-        <v>562.5</v>
+        <f aca="false">(C14*Assumptions!$G$43*Assumptions!$F$43+C16*Assumptions!$G$45*Assumptions!$F$45)*Assumptions!B$60/1000*INDEX(Assumptions!$B$80:$D$80,Assumptions!$B$5)*INDEX(Assumptions!$B$81:$D$81,Assumptions!$B$5)+(C5+C7)*Assumptions!B$91*INDEX(Assumptions!$B$82:$D$82,Assumptions!$B$5)</f>
+        <v>573.42</v>
       </c>
       <c r="D39" s="25" t="n">
-        <f aca="false">(D5+D7)*Assumptions!C$85*INDEX(Assumptions!$B$76:$D$76,Assumptions!$B$5)</f>
-        <v>3375</v>
+        <f aca="false">(D14*Assumptions!$G$43*Assumptions!$F$43+D16*Assumptions!$G$45*Assumptions!$F$45)*Assumptions!C$60/1000*INDEX(Assumptions!$B$80:$D$80,Assumptions!$B$5)*INDEX(Assumptions!$B$81:$D$81,Assumptions!$B$5)+(D5+D7)*Assumptions!C$91*INDEX(Assumptions!$B$82:$D$82,Assumptions!$B$5)</f>
+        <v>3030.39</v>
       </c>
       <c r="E39" s="25" t="n">
-        <f aca="false">(E5+E7)*Assumptions!D$85*INDEX(Assumptions!$B$76:$D$76,Assumptions!$B$5)</f>
-        <v>26250</v>
+        <f aca="false">(E14*Assumptions!$G$43*Assumptions!$F$43+E16*Assumptions!$G$45*Assumptions!$F$45)*Assumptions!D$60/1000*INDEX(Assumptions!$B$80:$D$80,Assumptions!$B$5)*INDEX(Assumptions!$B$81:$D$81,Assumptions!$B$5)+(E5+E7)*Assumptions!D$91*INDEX(Assumptions!$B$82:$D$82,Assumptions!$B$5)</f>
+        <v>17677.275</v>
       </c>
       <c r="F39" s="25" t="n">
-        <f aca="false">(F5+F7)*Assumptions!E$85*INDEX(Assumptions!$B$76:$D$76,Assumptions!$B$5)</f>
-        <v>146250</v>
+        <f aca="false">(F14*Assumptions!$G$43*Assumptions!$F$43+F16*Assumptions!$G$45*Assumptions!$F$45)*Assumptions!E$60/1000*INDEX(Assumptions!$B$80:$D$80,Assumptions!$B$5)*INDEX(Assumptions!$B$81:$D$81,Assumptions!$B$5)+(F5+F7)*Assumptions!E$91*INDEX(Assumptions!$B$82:$D$82,Assumptions!$B$5)</f>
+        <v>87544.6</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="24" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="25" t="n">
-        <f aca="false">Assumptions!B$86*INDEX(Assumptions!$B$77:$D$77,Assumptions!$B$5)</f>
+        <f aca="false">Assumptions!B$92*INDEX(Assumptions!$B$83:$D$83,Assumptions!$B$5)</f>
         <v>0</v>
       </c>
       <c r="D40" s="25" t="n">
-        <f aca="false">Assumptions!C$86*INDEX(Assumptions!$B$77:$D$77,Assumptions!$B$5)</f>
+        <f aca="false">Assumptions!C$92*INDEX(Assumptions!$B$83:$D$83,Assumptions!$B$5)</f>
         <v>2000</v>
       </c>
       <c r="E40" s="25" t="n">
-        <f aca="false">Assumptions!D$86*INDEX(Assumptions!$B$77:$D$77,Assumptions!$B$5)</f>
+        <f aca="false">Assumptions!D$92*INDEX(Assumptions!$B$83:$D$83,Assumptions!$B$5)</f>
         <v>10000</v>
       </c>
       <c r="F40" s="25" t="n">
-        <f aca="false">Assumptions!E$86*INDEX(Assumptions!$B$77:$D$77,Assumptions!$B$5)</f>
+        <f aca="false">Assumptions!E$92*INDEX(Assumptions!$B$83:$D$83,Assumptions!$B$5)</f>
         <v>40000</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="24" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="25" t="n">
-        <f aca="false">Assumptions!B$87*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)</f>
+        <f aca="false">Assumptions!B$93*INDEX(Assumptions!$B$84:$D$84,Assumptions!$B$5)</f>
         <v>0</v>
       </c>
       <c r="D41" s="25" t="n">
-        <f aca="false">Assumptions!C$87*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)</f>
+        <f aca="false">Assumptions!C$93*INDEX(Assumptions!$B$84:$D$84,Assumptions!$B$5)</f>
         <v>0</v>
       </c>
       <c r="E41" s="25" t="n">
-        <f aca="false">Assumptions!D$87*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)</f>
+        <f aca="false">Assumptions!D$93*INDEX(Assumptions!$B$84:$D$84,Assumptions!$B$5)</f>
         <v>4500</v>
       </c>
       <c r="F41" s="25" t="n">
-        <f aca="false">Assumptions!E$87*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)</f>
+        <f aca="false">Assumptions!E$93*INDEX(Assumptions!$B$84:$D$84,Assumptions!$B$5)</f>
         <v>22500</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="24" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="25" t="n">
-        <f aca="false">Assumptions!B$88*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)</f>
+        <f aca="false">Assumptions!B$94*INDEX(Assumptions!$B$85:$D$85,Assumptions!$B$5)</f>
         <v>3000</v>
       </c>
       <c r="D42" s="25" t="n">
-        <f aca="false">Assumptions!C$88*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)</f>
+        <f aca="false">Assumptions!C$94*INDEX(Assumptions!$B$85:$D$85,Assumptions!$B$5)</f>
         <v>6000</v>
       </c>
       <c r="E42" s="25" t="n">
-        <f aca="false">Assumptions!D$88*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)</f>
+        <f aca="false">Assumptions!D$94*INDEX(Assumptions!$B$85:$D$85,Assumptions!$B$5)</f>
         <v>9000</v>
       </c>
       <c r="F42" s="25" t="n">
-        <f aca="false">Assumptions!E$88*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)</f>
+        <f aca="false">Assumptions!E$94*INDEX(Assumptions!$B$85:$D$85,Assumptions!$B$5)</f>
         <v>12000</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="24" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="25" t="n">
-        <f aca="false">Assumptions!B$89*INDEX(Assumptions!$B$80:$D$80,Assumptions!$B$5)*Assumptions!$B$81</f>
+        <f aca="false">Assumptions!B$95*INDEX(Assumptions!$B$86:$D$86,Assumptions!$B$5)*Assumptions!$B$87</f>
         <v>0</v>
       </c>
       <c r="D43" s="25" t="n">
-        <f aca="false">Assumptions!C$89*INDEX(Assumptions!$B$80:$D$80,Assumptions!$B$5)*Assumptions!$B$81</f>
+        <f aca="false">Assumptions!C$95*INDEX(Assumptions!$B$86:$D$86,Assumptions!$B$5)*Assumptions!$B$87</f>
         <v>175</v>
       </c>
       <c r="E43" s="25" t="n">
-        <f aca="false">Assumptions!D$89*INDEX(Assumptions!$B$80:$D$80,Assumptions!$B$5)*Assumptions!$B$81</f>
+        <f aca="false">Assumptions!D$95*INDEX(Assumptions!$B$86:$D$86,Assumptions!$B$5)*Assumptions!$B$87</f>
         <v>1750</v>
       </c>
       <c r="F43" s="25" t="n">
-        <f aca="false">Assumptions!E$89*INDEX(Assumptions!$B$80:$D$80,Assumptions!$B$5)*Assumptions!$B$81</f>
+        <f aca="false">Assumptions!E$95*INDEX(Assumptions!$B$86:$D$86,Assumptions!$B$5)*Assumptions!$B$87</f>
         <v>10500</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="28" t="s">
-        <v>198</v>
+      <c r="A44" s="27" t="s">
+        <v>206</v>
       </c>
       <c r="B44" s="2"/>
-      <c r="C44" s="29" t="n">
+      <c r="C44" s="28" t="n">
         <f aca="false">SUM(C38:C43)</f>
-        <v>4015.8732</v>
-      </c>
-      <c r="D44" s="29" t="n">
+        <v>3848.55486</v>
+      </c>
+      <c r="D44" s="28" t="n">
         <f aca="false">SUM(D38:D43)</f>
-        <v>13203.3234</v>
-      </c>
-      <c r="E44" s="29" t="n">
+        <v>12263.18817</v>
+      </c>
+      <c r="E44" s="28" t="n">
         <f aca="false">SUM(E38:E43)</f>
-        <v>60812.165</v>
-      </c>
-      <c r="F44" s="29" t="n">
+        <v>48420.51275</v>
+      </c>
+      <c r="F44" s="28" t="n">
         <f aca="false">SUM(F38:F43)</f>
-        <v>275573.524</v>
+        <v>197817.1616</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="28" t="s">
-        <v>199</v>
+      <c r="A45" s="27" t="s">
+        <v>207</v>
       </c>
       <c r="B45" s="2"/>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="28" t="n">
         <f aca="false">C44-C33</f>
-        <v>3362.472650969</v>
-      </c>
-      <c r="D45" s="29" t="n">
+        <v>2416.814310969</v>
+      </c>
+      <c r="D45" s="28" t="n">
         <f aca="false">D44-D33</f>
-        <v>11150.696059813</v>
-      </c>
-      <c r="E45" s="29" t="n">
+        <v>9436.880829813</v>
+      </c>
+      <c r="E45" s="28" t="n">
         <f aca="false">E44-E33</f>
-        <v>53718.771884904</v>
-      </c>
-      <c r="F45" s="29" t="n">
+        <v>39812.449634904</v>
+      </c>
+      <c r="F45" s="28" t="n">
         <f aca="false">F44-F33</f>
-        <v>254801.272194753</v>
+        <v>170094.065794753</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="24" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B46" s="2"/>
-      <c r="C46" s="30" t="n">
+      <c r="C46" s="29" t="n">
         <f aca="false">IF(C44=0,0,C45/C44)</f>
-        <v>0.837295522918652</v>
-      </c>
-      <c r="D46" s="30" t="n">
+        <v>0.627979695986197</v>
+      </c>
+      <c r="D46" s="29" t="n">
         <f aca="false">IF(D44=0,0,D45/D44)</f>
-        <v>0.844537070099563</v>
-      </c>
-      <c r="E46" s="30" t="n">
+        <v>0.769529154979361</v>
+      </c>
+      <c r="E46" s="29" t="n">
         <f aca="false">IF(E44=0,0,E45/E44)</f>
-        <v>0.883355688535411</v>
-      </c>
-      <c r="F46" s="30" t="n">
+        <v>0.822222801325126</v>
+      </c>
+      <c r="F46" s="29" t="n">
         <f aca="false">IF(F44=0,0,F45/F44)</f>
-        <v>0.92462174339634</v>
+        <v>0.859854951001142</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="24" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B47" s="2"/>
-      <c r="C47" s="30" t="n">
+      <c r="C47" s="29" t="n">
         <f aca="false">IF(C44=0,0,C38/C44)</f>
-        <v>0.112895297590571</v>
-      </c>
-      <c r="D47" s="30" t="n">
+        <v>0.0714904347238537</v>
+      </c>
+      <c r="D47" s="29" t="n">
         <f aca="false">IF(D44=0,0,D38/D44)</f>
-        <v>0.125220245684507</v>
-      </c>
-      <c r="E47" s="30" t="n">
+        <v>0.0862580069176253</v>
+      </c>
+      <c r="E47" s="29" t="n">
         <f aca="false">IF(E44=0,0,E38/E44)</f>
-        <v>0.153129969965713</v>
-      </c>
-      <c r="F47" s="30" t="n">
+        <v>0.113448566279381</v>
+      </c>
+      <c r="F47" s="29" t="n">
         <f aca="false">IF(F44=0,0,F38/F44)</f>
-        <v>0.160841010256123</v>
+        <v>0.127757174330015</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="26" t="n">
         <f aca="false">C45*12</f>
-        <v>40349.671811628</v>
+        <v>29001.771731628</v>
       </c>
       <c r="D48" s="26" t="n">
         <f aca="false">D45*12</f>
-        <v>133808.352717756</v>
+        <v>113242.569957756</v>
       </c>
       <c r="E48" s="26" t="n">
         <f aca="false">E45*12</f>
-        <v>644625.262618848</v>
+        <v>477749.395618848</v>
       </c>
       <c r="F48" s="26" t="n">
         <f aca="false">F45*12</f>
-        <v>3057615.26633704</v>
+        <v>2041128.78953704</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="24" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="25" t="n">
         <f aca="false">C38+C39+C43</f>
-        <v>1015.8732</v>
+        <v>848.55486</v>
       </c>
       <c r="D49" s="25" t="n">
         <f aca="false">D38+D39+D43</f>
-        <v>5203.3234</v>
+        <v>4263.18817</v>
       </c>
       <c r="E49" s="25" t="n">
         <f aca="false">E38+E39+E43</f>
-        <v>37312.165</v>
+        <v>24920.51275</v>
       </c>
       <c r="F49" s="25" t="n">
         <f aca="false">F38+F39+F43</f>
-        <v>201073.524</v>
+        <v>123317.1616</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="28" t="s">
-        <v>204</v>
+      <c r="A50" s="27" t="s">
+        <v>212</v>
       </c>
       <c r="B50" s="2"/>
-      <c r="C50" s="29" t="n">
+      <c r="C50" s="28" t="n">
         <f aca="false">C49-C33</f>
-        <v>362.472650969</v>
-      </c>
-      <c r="D50" s="29" t="n">
+        <v>-583.185689031</v>
+      </c>
+      <c r="D50" s="28" t="n">
         <f aca="false">D49-D33</f>
-        <v>3150.696059813</v>
-      </c>
-      <c r="E50" s="29" t="n">
+        <v>1436.880829813</v>
+      </c>
+      <c r="E50" s="28" t="n">
         <f aca="false">E49-E33</f>
-        <v>30218.771884904</v>
-      </c>
-      <c r="F50" s="29" t="n">
+        <v>16312.449634904</v>
+      </c>
+      <c r="F50" s="28" t="n">
         <f aca="false">F49-F33</f>
-        <v>180301.272194753</v>
+        <v>95594.065794753</v>
       </c>
     </row>
   </sheetData>
@@ -5589,7 +5781,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -5606,7 +5798,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5624,7 +5816,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5658,58 +5850,58 @@
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="N4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -5733,21 +5925,21 @@
         <v>14863.475805247</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -5756,7 +5948,7 @@
       <c r="I6" s="2"/>
       <c r="J6" s="7" t="n">
         <f aca="false">Scenarios!C29</f>
-        <v>189.33</v>
+        <v>299</v>
       </c>
       <c r="K6" s="7" t="n">
         <f aca="false">Scenarios!D29</f>
@@ -5768,24 +5960,24 @@
       </c>
       <c r="M6" s="7" t="n">
         <f aca="false">Scenarios!F29</f>
-        <v>5116.776</v>
+        <v>8159.95</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E7" s="13" t="n">
         <v>49</v>
@@ -5797,10 +5989,10 @@
         <v>2</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J7" s="25" t="n">
         <f aca="false">$E7*F7</f>
@@ -5812,31 +6004,31 @@
       </c>
       <c r="L7" s="25" t="n">
         <f aca="false">$E7*H7</f>
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="M7" s="25" t="n">
         <f aca="false">$E7*I7</f>
-        <v>490</v>
+        <v>980</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>78</v>
+        <v>500</v>
       </c>
       <c r="F8" s="10" t="n">
         <v>1</v>
@@ -5852,36 +6044,36 @@
       </c>
       <c r="J8" s="25" t="n">
         <f aca="false">$E8*F8</f>
-        <v>78</v>
+        <v>500</v>
       </c>
       <c r="K8" s="25" t="n">
         <f aca="false">$E8*G8</f>
-        <v>78</v>
+        <v>500</v>
       </c>
       <c r="L8" s="25" t="n">
         <f aca="false">$E8*H8</f>
-        <v>156</v>
+        <v>1000</v>
       </c>
       <c r="M8" s="25" t="n">
         <f aca="false">$E8*I8</f>
-        <v>234</v>
+        <v>1500</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>229</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>0</v>
@@ -5915,27 +6107,27 @@
         <v>0</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E10" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" s="10" t="n">
         <v>0</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>1</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>1</v>
@@ -5952,32 +6144,32 @@
       </c>
       <c r="K10" s="25" t="n">
         <f aca="false">$E10*G10</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L10" s="25" t="n">
         <f aca="false">$E10*H10</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M10" s="25" t="n">
         <f aca="false">$E10*I10</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>0</v>
@@ -6011,30 +6203,30 @@
         <v>0</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H12" s="10" t="n">
         <v>500</v>
@@ -6044,36 +6236,36 @@
       </c>
       <c r="J12" s="25" t="n">
         <f aca="false">$E12*F12</f>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="K12" s="25" t="n">
         <f aca="false">$E12*G12</f>
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="L12" s="25" t="n">
         <f aca="false">$E12*H12</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M12" s="25" t="n">
         <f aca="false">$E12*I12</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>19.99</v>
@@ -6082,7 +6274,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="10" t="n">
         <v>0</v>
@@ -6096,7 +6288,7 @@
       </c>
       <c r="K13" s="25" t="n">
         <f aca="false">$E13*G13</f>
-        <v>19.99</v>
+        <v>0</v>
       </c>
       <c r="L13" s="25" t="n">
         <f aca="false">$E13*H13</f>
@@ -6107,24 +6299,24 @@
         <v>0</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>8</v>
+        <v>66.67</v>
       </c>
       <c r="F14" s="10" t="n">
         <v>1</v>
@@ -6140,36 +6332,36 @@
       </c>
       <c r="J14" s="25" t="n">
         <f aca="false">$E14*F14</f>
-        <v>8</v>
+        <v>66.67</v>
       </c>
       <c r="K14" s="25" t="n">
         <f aca="false">$E14*G14</f>
-        <v>8</v>
+        <v>66.67</v>
       </c>
       <c r="L14" s="25" t="n">
         <f aca="false">$E14*H14</f>
-        <v>8</v>
+        <v>66.67</v>
       </c>
       <c r="M14" s="25" t="n">
         <f aca="false">$E14*I14</f>
-        <v>8</v>
+        <v>66.67</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>30</v>
@@ -6184,7 +6376,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="25" t="n">
         <f aca="false">$E15*F15</f>
@@ -6200,27 +6392,27 @@
       </c>
       <c r="M15" s="25" t="n">
         <f aca="false">$E15*I15</f>
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F16" s="10" t="n">
         <v>1</v>
@@ -6232,139 +6424,177 @@
         <v>1</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" s="25" t="n">
         <f aca="false">$E16*F16</f>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K16" s="25" t="n">
         <f aca="false">$E16*G16</f>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L16" s="25" t="n">
         <f aca="false">$E16*H16</f>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M16" s="25" t="n">
         <f aca="false">$E16*I16</f>
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="I17" s="10" t="n">
-        <v>8000</v>
+        <v>1</v>
       </c>
       <c r="J17" s="25" t="n">
         <f aca="false">$E17*F17</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K17" s="25" t="n">
         <f aca="false">$E17*G17</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L17" s="25" t="n">
         <f aca="false">$E17*H17</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M17" s="25" t="n">
         <f aca="false">$E17*I17</f>
+        <v>30</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" s="25" t="n">
+        <f aca="false">$E18*F18</f>
+        <v>15</v>
+      </c>
+      <c r="K18" s="25" t="n">
+        <f aca="false">$E18*G18</f>
+        <v>15</v>
+      </c>
+      <c r="L18" s="25" t="n">
+        <f aca="false">$E18*H18</f>
+        <v>15</v>
+      </c>
+      <c r="M18" s="25" t="n">
+        <f aca="false">$E18*I18</f>
+        <v>30</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="N17" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-      <c r="B18" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="26" t="n">
-        <f aca="false">SUM(J7:J17)</f>
-        <v>199.99</v>
-      </c>
-      <c r="K18" s="26" t="n">
-        <f aca="false">SUM(K7:K17)</f>
-        <v>248.99</v>
-      </c>
-      <c r="L18" s="26" t="n">
-        <f aca="false">SUM(L7:L17)</f>
-        <v>405</v>
-      </c>
-      <c r="M18" s="26" t="n">
-        <f aca="false">SUM(M7:M17)</f>
-        <v>792</v>
-      </c>
-      <c r="N18" s="2"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
-      <c r="B19" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="29" t="n">
-        <f aca="false">SUM(J5:J6)+J18</f>
-        <v>653.400549031</v>
-      </c>
-      <c r="K19" s="29" t="n">
-        <f aca="false">SUM(K5:K6)+K18</f>
-        <v>2052.627340187</v>
-      </c>
-      <c r="L19" s="29" t="n">
-        <f aca="false">SUM(L5:L6)+L18</f>
-        <v>7093.393115096</v>
-      </c>
-      <c r="M19" s="29" t="n">
-        <f aca="false">SUM(M5:M6)+M18</f>
-        <v>20772.251805247</v>
-      </c>
-      <c r="N19" s="2"/>
+      <c r="F19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I19" s="10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J19" s="25" t="n">
+        <f aca="false">$E19*F19</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="25" t="n">
+        <f aca="false">$E19*G19</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="25" t="n">
+        <f aca="false">$E19*H19</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="25" t="n">
+        <f aca="false">$E19*I19</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
+      <c r="B20" s="4" t="s">
+        <v>281</v>
+      </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -6372,17 +6602,29 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
+      <c r="J20" s="26" t="n">
+        <f aca="false">SUM(J7:J19)</f>
+        <v>868.66</v>
+      </c>
+      <c r="K20" s="26" t="n">
+        <f aca="false">SUM(K7:K19)</f>
+        <v>1022.67</v>
+      </c>
+      <c r="L20" s="26" t="n">
+        <f aca="false">SUM(L7:L19)</f>
+        <v>1919.67</v>
+      </c>
+      <c r="M20" s="26" t="n">
+        <f aca="false">SUM(M7:M19)</f>
+        <v>4699.67</v>
+      </c>
       <c r="N20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="B21" s="2"/>
+      <c r="A21" s="2"/>
+      <c r="B21" s="4" t="s">
+        <v>282</v>
+      </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -6390,48 +6632,48 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
+      <c r="J21" s="28" t="n">
+        <f aca="false">SUM(J5:J6)+J20</f>
+        <v>1431.740549031</v>
+      </c>
+      <c r="K21" s="28" t="n">
+        <f aca="false">SUM(K5:K6)+K20</f>
+        <v>2826.307340187</v>
+      </c>
+      <c r="L21" s="28" t="n">
+        <f aca="false">SUM(L5:L6)+L20</f>
+        <v>8608.063115096</v>
+      </c>
+      <c r="M21" s="28" t="n">
+        <f aca="false">SUM(M5:M6)+M20</f>
+        <v>27723.095805247</v>
+      </c>
       <c r="N21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5" t="s">
-        <v>269</v>
-      </c>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
       <c r="N22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>271</v>
-      </c>
+      <c r="A23" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="20" t="n">
-        <v>1500</v>
-      </c>
+      <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
@@ -6439,46 +6681,44 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
-      <c r="M23" s="2" t="s">
-        <v>272</v>
-      </c>
+      <c r="M23" s="2"/>
       <c r="N23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="20" t="n">
-        <v>700</v>
-      </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2" t="s">
-        <v>274</v>
+      <c r="A24" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5" t="s">
+        <v>285</v>
       </c>
       <c r="N24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="20" t="n">
-        <v>50</v>
+        <v>5000</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -6488,21 +6728,21 @@
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="N25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="20" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -6512,21 +6752,21 @@
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2" t="s">
-        <v>256</v>
+        <v>289</v>
       </c>
       <c r="N26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="20" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -6536,21 +6776,21 @@
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2" t="s">
-        <v>256</v>
+        <v>291</v>
       </c>
       <c r="N27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="20" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -6560,20 +6800,21 @@
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="N28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2"/>
-      <c r="B29" s="4" t="s">
-        <v>282</v>
+      <c r="A29" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>295</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
-      <c r="E29" s="26" t="n">
-        <f aca="false">SUM(E23:E28)</f>
-        <v>2770</v>
+      <c r="E29" s="20" t="n">
+        <v>500</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -6582,8 +6823,79 @@
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
+      <c r="M29" s="2" t="s">
+        <v>272</v>
+      </c>
       <c r="N29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="N30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="N31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2"/>
+      <c r="B32" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="26" t="n">
+        <f aca="false">SUM(E25:E31)</f>
+        <v>7340</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6617,7 +6929,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6634,7 +6946,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6666,43 +6978,43 @@
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6710,40 +7022,40 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">Assumptions!B$93</f>
+        <f aca="false">Assumptions!B$99</f>
         <v>1</v>
       </c>
       <c r="C5" s="8" t="n">
-        <f aca="false">Assumptions!B$94</f>
+        <f aca="false">Assumptions!B$100</f>
         <v>0.1</v>
       </c>
       <c r="D5" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$33:$F$33,B5)</f>
-        <v>653.400549031</v>
+        <v>1431.740549031</v>
       </c>
       <c r="E5" s="25" t="n">
-        <f aca="false">'Cost Lines'!$E$29</f>
-        <v>2770</v>
+        <f aca="false">'Cost Lines'!$E$32</f>
+        <v>7340</v>
       </c>
       <c r="F5" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$38:$F$38,B5)*C5</f>
-        <v>45.33732</v>
+        <v>27.513486</v>
       </c>
       <c r="G5" s="25" t="n">
         <f aca="false">(INDEX(Scenarios!$C$44:$F$44,B5)-INDEX(Scenarios!$C$38:$F$38,B5))*C5</f>
-        <v>356.25</v>
+        <v>357.342</v>
       </c>
       <c r="H5" s="25" t="n">
         <f aca="false">F5+G5</f>
-        <v>401.58732</v>
+        <v>384.855486</v>
       </c>
       <c r="I5" s="26" t="n">
         <f aca="false">H5-D5-E5</f>
-        <v>-3021.813229031</v>
+        <v>-8386.885063031</v>
       </c>
       <c r="J5" s="26" t="n">
         <f aca="false">I5</f>
-        <v>-3021.813229031</v>
+        <v>-8386.885063031</v>
       </c>
       <c r="K5" s="23" t="str">
         <f aca="false">IF(J5&gt;=0,IF(TRUE(),A5,""),"")</f>
@@ -6751,11 +7063,11 @@
       </c>
       <c r="L5" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$49:$F$49,B5)*C5-D5-E5</f>
-        <v>-3321.813229031</v>
+        <v>-8686.885063031</v>
       </c>
       <c r="M5" s="25" t="n">
         <f aca="false">L5</f>
-        <v>-3321.813229031</v>
+        <v>-8686.885063031</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6763,16 +7075,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">Assumptions!C$93</f>
+        <f aca="false">Assumptions!C$99</f>
         <v>1</v>
       </c>
       <c r="C6" s="8" t="n">
-        <f aca="false">Assumptions!C$94</f>
+        <f aca="false">Assumptions!C$100</f>
         <v>0.2</v>
       </c>
       <c r="D6" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$33:$F$33,B6)</f>
-        <v>653.400549031</v>
+        <v>1431.740549031</v>
       </c>
       <c r="E6" s="25" t="n">
         <f aca="false">0</f>
@@ -6780,23 +7092,23 @@
       </c>
       <c r="F6" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$38:$F$38,B6)*C6</f>
-        <v>90.67464</v>
+        <v>55.026972</v>
       </c>
       <c r="G6" s="25" t="n">
         <f aca="false">(INDEX(Scenarios!$C$44:$F$44,B6)-INDEX(Scenarios!$C$38:$F$38,B6))*C6</f>
-        <v>712.5</v>
+        <v>714.684</v>
       </c>
       <c r="H6" s="25" t="n">
         <f aca="false">F6+G6</f>
-        <v>803.17464</v>
+        <v>769.710972</v>
       </c>
       <c r="I6" s="26" t="n">
         <f aca="false">H6-D6-E6</f>
-        <v>149.774090969</v>
+        <v>-662.029577031</v>
       </c>
       <c r="J6" s="26" t="n">
         <f aca="false">J5+I6</f>
-        <v>-2872.039138062</v>
+        <v>-9048.914640062</v>
       </c>
       <c r="K6" s="23" t="str">
         <f aca="false">IF(J6&gt;=0,IF(J5&lt;0,A6,""),"")</f>
@@ -6804,11 +7116,11 @@
       </c>
       <c r="L6" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$49:$F$49,B6)*C6-D6-E6</f>
-        <v>-450.225909031</v>
+        <v>-1262.029577031</v>
       </c>
       <c r="M6" s="25" t="n">
         <f aca="false">M5+L6</f>
-        <v>-3772.039138062</v>
+        <v>-9948.914640062</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6816,16 +7128,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">Assumptions!D$93</f>
+        <f aca="false">Assumptions!D$99</f>
         <v>1</v>
       </c>
       <c r="C7" s="8" t="n">
-        <f aca="false">Assumptions!D$94</f>
+        <f aca="false">Assumptions!D$100</f>
         <v>0.3</v>
       </c>
       <c r="D7" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$33:$F$33,B7)</f>
-        <v>653.400549031</v>
+        <v>1431.740549031</v>
       </c>
       <c r="E7" s="25" t="n">
         <f aca="false">0</f>
@@ -6833,23 +7145,23 @@
       </c>
       <c r="F7" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$38:$F$38,B7)*C7</f>
-        <v>136.01196</v>
+        <v>82.540458</v>
       </c>
       <c r="G7" s="25" t="n">
         <f aca="false">(INDEX(Scenarios!$C$44:$F$44,B7)-INDEX(Scenarios!$C$38:$F$38,B7))*C7</f>
-        <v>1068.75</v>
+        <v>1072.026</v>
       </c>
       <c r="H7" s="25" t="n">
         <f aca="false">F7+G7</f>
-        <v>1204.76196</v>
+        <v>1154.566458</v>
       </c>
       <c r="I7" s="26" t="n">
         <f aca="false">H7-D7-E7</f>
-        <v>551.361410969</v>
+        <v>-277.174091031</v>
       </c>
       <c r="J7" s="26" t="n">
         <f aca="false">J6+I7</f>
-        <v>-2320.677727093</v>
+        <v>-9326.088731093</v>
       </c>
       <c r="K7" s="23" t="str">
         <f aca="false">IF(J7&gt;=0,IF(J6&lt;0,A7,""),"")</f>
@@ -6857,11 +7169,11 @@
       </c>
       <c r="L7" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$49:$F$49,B7)*C7-D7-E7</f>
-        <v>-348.638589031</v>
+        <v>-1177.174091031</v>
       </c>
       <c r="M7" s="25" t="n">
         <f aca="false">M6+L7</f>
-        <v>-4120.677727093</v>
+        <v>-11126.088731093</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6869,16 +7181,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="6" t="n">
-        <f aca="false">Assumptions!E$93</f>
+        <f aca="false">Assumptions!E$99</f>
         <v>2</v>
       </c>
       <c r="C8" s="8" t="n">
-        <f aca="false">Assumptions!E$94</f>
+        <f aca="false">Assumptions!E$100</f>
         <v>0.35</v>
       </c>
       <c r="D8" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$33:$F$33,B8)</f>
-        <v>2052.627340187</v>
+        <v>2826.307340187</v>
       </c>
       <c r="E8" s="25" t="n">
         <f aca="false">0</f>
@@ -6886,35 +7198,35 @@
       </c>
       <c r="F8" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$38:$F$38,B8)*C8</f>
-        <v>578.66319</v>
+        <v>370.2293595</v>
       </c>
       <c r="G8" s="25" t="n">
         <f aca="false">(INDEX(Scenarios!$C$44:$F$44,B8)-INDEX(Scenarios!$C$38:$F$38,B8))*C8</f>
-        <v>4042.5</v>
+        <v>3921.8865</v>
       </c>
       <c r="H8" s="25" t="n">
         <f aca="false">F8+G8</f>
-        <v>4621.16319</v>
+        <v>4292.1158595</v>
       </c>
       <c r="I8" s="26" t="n">
         <f aca="false">H8-D8-E8</f>
-        <v>2568.535849813</v>
+        <v>1465.808519313</v>
       </c>
       <c r="J8" s="26" t="n">
         <f aca="false">J7+I8</f>
-        <v>247.85812272</v>
-      </c>
-      <c r="K8" s="23" t="n">
+        <v>-7860.28021178</v>
+      </c>
+      <c r="K8" s="23" t="str">
         <f aca="false">IF(J8&gt;=0,IF(J7&lt;0,A8,""),"")</f>
-        <v>4</v>
+        <v/>
       </c>
       <c r="L8" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$49:$F$49,B8)*C8-D8-E8</f>
-        <v>-231.464150187</v>
+        <v>-1334.191480687</v>
       </c>
       <c r="M8" s="25" t="n">
         <f aca="false">M7+L8</f>
-        <v>-4352.14187728</v>
+        <v>-12460.28021178</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6922,16 +7234,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="n">
-        <f aca="false">Assumptions!F$93</f>
+        <f aca="false">Assumptions!F$99</f>
         <v>2</v>
       </c>
       <c r="C9" s="8" t="n">
-        <f aca="false">Assumptions!F$94</f>
+        <f aca="false">Assumptions!F$100</f>
         <v>0.45</v>
       </c>
       <c r="D9" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$33:$F$33,B9)</f>
-        <v>2052.627340187</v>
+        <v>2826.307340187</v>
       </c>
       <c r="E9" s="25" t="n">
         <f aca="false">0</f>
@@ -6939,23 +7251,23 @@
       </c>
       <c r="F9" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$38:$F$38,B9)*C9</f>
-        <v>743.99553</v>
+        <v>476.0091765</v>
       </c>
       <c r="G9" s="25" t="n">
         <f aca="false">(INDEX(Scenarios!$C$44:$F$44,B9)-INDEX(Scenarios!$C$38:$F$38,B9))*C9</f>
-        <v>5197.5</v>
+        <v>5042.4255</v>
       </c>
       <c r="H9" s="25" t="n">
         <f aca="false">F9+G9</f>
-        <v>5941.49553</v>
+        <v>5518.4346765</v>
       </c>
       <c r="I9" s="26" t="n">
         <f aca="false">H9-D9-E9</f>
-        <v>3888.868189813</v>
+        <v>2692.127336313</v>
       </c>
       <c r="J9" s="26" t="n">
         <f aca="false">J8+I9</f>
-        <v>4136.726312533</v>
+        <v>-5168.152875467</v>
       </c>
       <c r="K9" s="23" t="str">
         <f aca="false">IF(J9&gt;=0,IF(J8&lt;0,A9,""),"")</f>
@@ -6963,11 +7275,11 @@
       </c>
       <c r="L9" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$49:$F$49,B9)*C9-D9-E9</f>
-        <v>288.868189813</v>
+        <v>-907.872663687</v>
       </c>
       <c r="M9" s="25" t="n">
         <f aca="false">M8+L9</f>
-        <v>-4063.273687467</v>
+        <v>-13368.152875467</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6975,16 +7287,16 @@
         <v>6</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">Assumptions!G$93</f>
+        <f aca="false">Assumptions!G$99</f>
         <v>2</v>
       </c>
       <c r="C10" s="8" t="n">
-        <f aca="false">Assumptions!G$94</f>
+        <f aca="false">Assumptions!G$100</f>
         <v>0.55</v>
       </c>
       <c r="D10" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$33:$F$33,B10)</f>
-        <v>2052.627340187</v>
+        <v>2826.307340187</v>
       </c>
       <c r="E10" s="25" t="n">
         <f aca="false">0</f>
@@ -6992,23 +7304,23 @@
       </c>
       <c r="F10" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$38:$F$38,B10)*C10</f>
-        <v>909.32787</v>
+        <v>581.7889935</v>
       </c>
       <c r="G10" s="25" t="n">
         <f aca="false">(INDEX(Scenarios!$C$44:$F$44,B10)-INDEX(Scenarios!$C$38:$F$38,B10))*C10</f>
-        <v>6352.5</v>
+        <v>6162.9645</v>
       </c>
       <c r="H10" s="25" t="n">
         <f aca="false">F10+G10</f>
-        <v>7261.82787</v>
+        <v>6744.7534935</v>
       </c>
       <c r="I10" s="26" t="n">
         <f aca="false">H10-D10-E10</f>
-        <v>5209.200529813</v>
+        <v>3918.446153313</v>
       </c>
       <c r="J10" s="26" t="n">
         <f aca="false">J9+I10</f>
-        <v>9345.926842346</v>
+        <v>-1249.706722154</v>
       </c>
       <c r="K10" s="23" t="str">
         <f aca="false">IF(J10&gt;=0,IF(J9&lt;0,A10,""),"")</f>
@@ -7016,11 +7328,11 @@
       </c>
       <c r="L10" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$49:$F$49,B10)*C10-D10-E10</f>
-        <v>809.200529813001</v>
+        <v>-481.553846687</v>
       </c>
       <c r="M10" s="25" t="n">
         <f aca="false">M9+L10</f>
-        <v>-3254.073157654</v>
+        <v>-13849.706722154</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7028,16 +7340,16 @@
         <v>7</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">Assumptions!H$93</f>
+        <f aca="false">Assumptions!H$99</f>
         <v>3</v>
       </c>
       <c r="C11" s="8" t="n">
-        <f aca="false">Assumptions!H$94</f>
+        <f aca="false">Assumptions!H$100</f>
         <v>0.5</v>
       </c>
       <c r="D11" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$33:$F$33,B11)</f>
-        <v>7093.393115096</v>
+        <v>8608.063115096</v>
       </c>
       <c r="E11" s="25" t="n">
         <f aca="false">0</f>
@@ -7045,35 +7357,35 @@
       </c>
       <c r="F11" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$38:$F$38,B11)*C11</f>
-        <v>4656.0825</v>
+        <v>2746.618875</v>
       </c>
       <c r="G11" s="25" t="n">
         <f aca="false">(INDEX(Scenarios!$C$44:$F$44,B11)-INDEX(Scenarios!$C$38:$F$38,B11))*C11</f>
-        <v>25750</v>
+        <v>21463.6375</v>
       </c>
       <c r="H11" s="25" t="n">
         <f aca="false">F11+G11</f>
-        <v>30406.0825</v>
+        <v>24210.256375</v>
       </c>
       <c r="I11" s="26" t="n">
         <f aca="false">H11-D11-E11</f>
-        <v>23312.689384904</v>
+        <v>15602.193259904</v>
       </c>
       <c r="J11" s="26" t="n">
         <f aca="false">J10+I11</f>
-        <v>32658.61622725</v>
-      </c>
-      <c r="K11" s="23" t="str">
+        <v>14352.48653775</v>
+      </c>
+      <c r="K11" s="23" t="n">
         <f aca="false">IF(J11&gt;=0,IF(J10&lt;0,A11,""),"")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="L11" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$49:$F$49,B11)*C11-D11-E11</f>
-        <v>11562.689384904</v>
+        <v>3852.193259904</v>
       </c>
       <c r="M11" s="25" t="n">
         <f aca="false">M10+L11</f>
-        <v>8308.61622725</v>
+        <v>-9997.51346225</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7081,16 +7393,16 @@
         <v>8</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">Assumptions!I$93</f>
+        <f aca="false">Assumptions!I$99</f>
         <v>3</v>
       </c>
       <c r="C12" s="8" t="n">
-        <f aca="false">Assumptions!I$94</f>
+        <f aca="false">Assumptions!I$100</f>
         <v>0.6</v>
       </c>
       <c r="D12" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$33:$F$33,B12)</f>
-        <v>7093.393115096</v>
+        <v>8608.063115096</v>
       </c>
       <c r="E12" s="25" t="n">
         <f aca="false">0</f>
@@ -7098,23 +7410,23 @@
       </c>
       <c r="F12" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$38:$F$38,B12)*C12</f>
-        <v>5587.299</v>
+        <v>3295.94265</v>
       </c>
       <c r="G12" s="25" t="n">
         <f aca="false">(INDEX(Scenarios!$C$44:$F$44,B12)-INDEX(Scenarios!$C$38:$F$38,B12))*C12</f>
-        <v>30900</v>
+        <v>25756.365</v>
       </c>
       <c r="H12" s="25" t="n">
         <f aca="false">F12+G12</f>
-        <v>36487.299</v>
+        <v>29052.30765</v>
       </c>
       <c r="I12" s="26" t="n">
         <f aca="false">H12-D12-E12</f>
-        <v>29393.905884904</v>
+        <v>20444.244534904</v>
       </c>
       <c r="J12" s="26" t="n">
         <f aca="false">J11+I12</f>
-        <v>62052.522112154</v>
+        <v>34796.731072654</v>
       </c>
       <c r="K12" s="23" t="str">
         <f aca="false">IF(J12&gt;=0,IF(J11&lt;0,A12,""),"")</f>
@@ -7122,11 +7434,11 @@
       </c>
       <c r="L12" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$49:$F$49,B12)*C12-D12-E12</f>
-        <v>15293.905884904</v>
+        <v>6344.244534904</v>
       </c>
       <c r="M12" s="25" t="n">
         <f aca="false">M11+L12</f>
-        <v>23602.522112154</v>
+        <v>-3653.268927346</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7134,16 +7446,16 @@
         <v>9</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">Assumptions!J$93</f>
+        <f aca="false">Assumptions!J$99</f>
         <v>3</v>
       </c>
       <c r="C13" s="8" t="n">
-        <f aca="false">Assumptions!J$94</f>
+        <f aca="false">Assumptions!J$100</f>
         <v>0.7</v>
       </c>
       <c r="D13" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$33:$F$33,B13)</f>
-        <v>7093.393115096</v>
+        <v>8608.063115096</v>
       </c>
       <c r="E13" s="25" t="n">
         <f aca="false">0</f>
@@ -7151,23 +7463,23 @@
       </c>
       <c r="F13" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$38:$F$38,B13)*C13</f>
-        <v>6518.5155</v>
+        <v>3845.266425</v>
       </c>
       <c r="G13" s="25" t="n">
         <f aca="false">(INDEX(Scenarios!$C$44:$F$44,B13)-INDEX(Scenarios!$C$38:$F$38,B13))*C13</f>
-        <v>36050</v>
+        <v>30049.0925</v>
       </c>
       <c r="H13" s="25" t="n">
         <f aca="false">F13+G13</f>
-        <v>42568.5155</v>
+        <v>33894.358925</v>
       </c>
       <c r="I13" s="26" t="n">
         <f aca="false">H13-D13-E13</f>
-        <v>35475.122384904</v>
+        <v>25286.295809904</v>
       </c>
       <c r="J13" s="26" t="n">
         <f aca="false">J12+I13</f>
-        <v>97527.644497058</v>
+        <v>60083.026882558</v>
       </c>
       <c r="K13" s="23" t="str">
         <f aca="false">IF(J13&gt;=0,IF(J12&lt;0,A13,""),"")</f>
@@ -7175,11 +7487,11 @@
       </c>
       <c r="L13" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$49:$F$49,B13)*C13-D13-E13</f>
-        <v>19025.122384904</v>
+        <v>8836.295809904</v>
       </c>
       <c r="M13" s="25" t="n">
         <f aca="false">M12+L13</f>
-        <v>42627.644497058</v>
+        <v>5183.026882558</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7187,16 +7499,16 @@
         <v>10</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">Assumptions!K$93</f>
+        <f aca="false">Assumptions!K$99</f>
         <v>3</v>
       </c>
       <c r="C14" s="8" t="n">
-        <f aca="false">Assumptions!K$94</f>
+        <f aca="false">Assumptions!K$100</f>
         <v>0.8</v>
       </c>
       <c r="D14" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$33:$F$33,B14)</f>
-        <v>7093.393115096</v>
+        <v>8608.063115096</v>
       </c>
       <c r="E14" s="25" t="n">
         <f aca="false">0</f>
@@ -7204,23 +7516,23 @@
       </c>
       <c r="F14" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$38:$F$38,B14)*C14</f>
-        <v>7449.732</v>
+        <v>4394.5902</v>
       </c>
       <c r="G14" s="25" t="n">
         <f aca="false">(INDEX(Scenarios!$C$44:$F$44,B14)-INDEX(Scenarios!$C$38:$F$38,B14))*C14</f>
-        <v>41200</v>
+        <v>34341.82</v>
       </c>
       <c r="H14" s="25" t="n">
         <f aca="false">F14+G14</f>
-        <v>48649.732</v>
+        <v>38736.4102</v>
       </c>
       <c r="I14" s="26" t="n">
         <f aca="false">H14-D14-E14</f>
-        <v>41556.338884904</v>
+        <v>30128.347084904</v>
       </c>
       <c r="J14" s="26" t="n">
         <f aca="false">J13+I14</f>
-        <v>139083.983381962</v>
+        <v>90211.373967462</v>
       </c>
       <c r="K14" s="23" t="str">
         <f aca="false">IF(J14&gt;=0,IF(J13&lt;0,A14,""),"")</f>
@@ -7228,11 +7540,11 @@
       </c>
       <c r="L14" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$49:$F$49,B14)*C14-D14-E14</f>
-        <v>22756.338884904</v>
+        <v>11328.347084904</v>
       </c>
       <c r="M14" s="25" t="n">
         <f aca="false">M13+L14</f>
-        <v>65383.983381962</v>
+        <v>16511.373967462</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7240,16 +7552,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="6" t="n">
-        <f aca="false">Assumptions!L$93</f>
+        <f aca="false">Assumptions!L$99</f>
         <v>3</v>
       </c>
       <c r="C15" s="8" t="n">
-        <f aca="false">Assumptions!L$94</f>
+        <f aca="false">Assumptions!L$100</f>
         <v>0.9</v>
       </c>
       <c r="D15" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$33:$F$33,B15)</f>
-        <v>7093.393115096</v>
+        <v>8608.063115096</v>
       </c>
       <c r="E15" s="25" t="n">
         <f aca="false">0</f>
@@ -7257,23 +7569,23 @@
       </c>
       <c r="F15" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$38:$F$38,B15)*C15</f>
-        <v>8380.9485</v>
+        <v>4943.913975</v>
       </c>
       <c r="G15" s="25" t="n">
         <f aca="false">(INDEX(Scenarios!$C$44:$F$44,B15)-INDEX(Scenarios!$C$38:$F$38,B15))*C15</f>
-        <v>46350</v>
+        <v>38634.5475</v>
       </c>
       <c r="H15" s="25" t="n">
         <f aca="false">F15+G15</f>
-        <v>54730.9485</v>
+        <v>43578.461475</v>
       </c>
       <c r="I15" s="26" t="n">
         <f aca="false">H15-D15-E15</f>
-        <v>47637.555384904</v>
+        <v>34970.398359904</v>
       </c>
       <c r="J15" s="26" t="n">
         <f aca="false">J14+I15</f>
-        <v>186721.538766866</v>
+        <v>125181.772327366</v>
       </c>
       <c r="K15" s="23" t="str">
         <f aca="false">IF(J15&gt;=0,IF(J14&lt;0,A15,""),"")</f>
@@ -7281,11 +7593,11 @@
       </c>
       <c r="L15" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$49:$F$49,B15)*C15-D15-E15</f>
-        <v>26487.555384904</v>
+        <v>13820.398359904</v>
       </c>
       <c r="M15" s="25" t="n">
         <f aca="false">M14+L15</f>
-        <v>91871.538766866</v>
+        <v>30331.772327366</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7293,16 +7605,16 @@
         <v>12</v>
       </c>
       <c r="B16" s="6" t="n">
-        <f aca="false">Assumptions!M$93</f>
+        <f aca="false">Assumptions!M$99</f>
         <v>3</v>
       </c>
       <c r="C16" s="8" t="n">
-        <f aca="false">Assumptions!M$94</f>
+        <f aca="false">Assumptions!M$100</f>
         <v>1</v>
       </c>
       <c r="D16" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$33:$F$33,B16)</f>
-        <v>7093.393115096</v>
+        <v>8608.063115096</v>
       </c>
       <c r="E16" s="25" t="n">
         <f aca="false">0</f>
@@ -7310,23 +7622,23 @@
       </c>
       <c r="F16" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$38:$F$38,B16)*C16</f>
-        <v>9312.165</v>
+        <v>5493.23775</v>
       </c>
       <c r="G16" s="25" t="n">
         <f aca="false">(INDEX(Scenarios!$C$44:$F$44,B16)-INDEX(Scenarios!$C$38:$F$38,B16))*C16</f>
-        <v>51500</v>
+        <v>42927.275</v>
       </c>
       <c r="H16" s="25" t="n">
         <f aca="false">F16+G16</f>
-        <v>60812.165</v>
+        <v>48420.51275</v>
       </c>
       <c r="I16" s="26" t="n">
         <f aca="false">H16-D16-E16</f>
-        <v>53718.771884904</v>
+        <v>39812.449634904</v>
       </c>
       <c r="J16" s="26" t="n">
         <f aca="false">J15+I16</f>
-        <v>240440.31065177</v>
+        <v>164994.22196227</v>
       </c>
       <c r="K16" s="23" t="str">
         <f aca="false">IF(J16&gt;=0,IF(J15&lt;0,A16,""),"")</f>
@@ -7334,11 +7646,11 @@
       </c>
       <c r="L16" s="25" t="n">
         <f aca="false">INDEX(Scenarios!$C$49:$F$49,B16)*C16-D16-E16</f>
-        <v>30218.771884904</v>
+        <v>16312.449634904</v>
       </c>
       <c r="M16" s="25" t="n">
         <f aca="false">M15+L16</f>
-        <v>122090.31065177</v>
+        <v>46644.22196227</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7358,7 +7670,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -7390,13 +7702,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
-      <c r="D20" s="31" t="n">
+      <c r="D20" s="30" t="n">
         <f aca="false">IF(COUNT(K5:K16)=0,"Not within 12 months",MIN(K5:K16))</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
@@ -7410,13 +7722,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
-      <c r="D21" s="32" t="n">
+      <c r="D21" s="31" t="n">
         <f aca="false">MIN(0,MIN(J5:J16))</f>
-        <v>-3021.813229031</v>
+        <v>-9326.088731093</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
@@ -7430,13 +7742,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="32" t="n">
+      <c r="D22" s="31" t="n">
         <f aca="false">SUM(H5:H16)</f>
-        <v>293888.75301</v>
+        <v>236756.7443205</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -7450,13 +7762,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
-      <c r="D23" s="32" t="n">
+      <c r="D23" s="31" t="n">
         <f aca="false">SUM(D5:D16)+SUM(E5:E16)</f>
-        <v>53448.44235823</v>
+        <v>71762.52235823</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -7470,13 +7782,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
-      <c r="D24" s="33" t="n">
+      <c r="D24" s="32" t="n">
         <f aca="false">IF(D23=0,0,(D22-D23)/D23)</f>
-        <v>4.49854663752885</v>
+        <v>2.29916976912599</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
@@ -7490,13 +7802,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
-      <c r="D25" s="32" t="n">
+      <c r="D25" s="31" t="n">
         <f aca="false">MIN(0,MIN(M5:M16))</f>
-        <v>-4352.14187728</v>
+        <v>-13849.706722154</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
@@ -7510,13 +7822,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
-      <c r="D26" s="32" t="n">
+      <c r="D26" s="31" t="n">
         <f aca="false">M16</f>
-        <v>122090.31065177</v>
+        <v>46644.22196227</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
@@ -7553,7 +7865,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7565,7 +7877,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7587,7 +7899,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="B4" s="10" t="n">
         <v>25</v>
@@ -7616,32 +7928,32 @@
         <v>5</v>
       </c>
       <c r="B5" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*B$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A5*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>44563.926884904</v>
+        <f aca="false">Scenarios!$E$21*B$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A5*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>34463.421884904</v>
       </c>
       <c r="C5" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*C$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A5*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>44721.246884904</v>
+        <f aca="false">Scenarios!$E$21*C$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A5*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>34607.631884904</v>
       </c>
       <c r="D5" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*D$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A5*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>45035.886884904</v>
+        <f aca="false">Scenarios!$E$21*D$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A5*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>34896.051884904</v>
       </c>
       <c r="E5" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*E$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A5*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>45979.806884904</v>
+        <f aca="false">Scenarios!$E$21*E$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A5*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>35761.311884904</v>
       </c>
       <c r="F5" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*F$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A5*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>47553.006884904</v>
+        <f aca="false">Scenarios!$E$21*F$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A5*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>37203.411884904</v>
       </c>
       <c r="G5" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*G$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A5*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>50699.406884904</v>
+        <f aca="false">Scenarios!$E$21*G$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A5*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>40087.611884904</v>
       </c>
       <c r="H5" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*H$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A5*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>60138.606884904</v>
+        <f aca="false">Scenarios!$E$21*H$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A5*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>48740.211884904</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7649,32 +7961,32 @@
         <v>8</v>
       </c>
       <c r="B6" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*B$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A6*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>44658.318884904</v>
+        <f aca="false">Scenarios!$E$21*B$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A6*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>34549.947884904</v>
       </c>
       <c r="C6" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*C$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A6*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>44910.030884904</v>
+        <f aca="false">Scenarios!$E$21*C$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A6*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>34780.683884904</v>
       </c>
       <c r="D6" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*D$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A6*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>45413.454884904</v>
+        <f aca="false">Scenarios!$E$21*D$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A6*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>35242.155884904</v>
       </c>
       <c r="E6" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*E$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A6*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>46923.726884904</v>
+        <f aca="false">Scenarios!$E$21*E$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A6*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>36626.571884904</v>
       </c>
       <c r="F6" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*F$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A6*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>49440.846884904</v>
+        <f aca="false">Scenarios!$E$21*F$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A6*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>38933.931884904</v>
       </c>
       <c r="G6" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*G$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A6*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>54475.086884904</v>
+        <f aca="false">Scenarios!$E$21*G$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A6*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>43548.651884904</v>
       </c>
       <c r="H6" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*H$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A6*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>69577.806884904</v>
+        <f aca="false">Scenarios!$E$21*H$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A6*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>57392.811884904</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7682,32 +7994,32 @@
         <v>10</v>
       </c>
       <c r="B7" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*B$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A7*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>44721.246884904</v>
+        <f aca="false">Scenarios!$E$21*B$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A7*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>34607.631884904</v>
       </c>
       <c r="C7" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*C$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A7*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>45035.886884904</v>
+        <f aca="false">Scenarios!$E$21*C$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A7*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>34896.051884904</v>
       </c>
       <c r="D7" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*D$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A7*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>45665.166884904</v>
+        <f aca="false">Scenarios!$E$21*D$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A7*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>35472.891884904</v>
       </c>
       <c r="E7" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*E$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A7*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>47553.006884904</v>
+        <f aca="false">Scenarios!$E$21*E$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A7*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>37203.411884904</v>
       </c>
       <c r="F7" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*F$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A7*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>50699.406884904</v>
+        <f aca="false">Scenarios!$E$21*F$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A7*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>40087.611884904</v>
       </c>
       <c r="G7" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*G$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A7*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>56992.206884904</v>
+        <f aca="false">Scenarios!$E$21*G$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A7*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>45856.011884904</v>
       </c>
       <c r="H7" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*H$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A7*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>75870.606884904</v>
+        <f aca="false">Scenarios!$E$21*H$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A7*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>63161.211884904</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7715,32 +8027,32 @@
         <v>15</v>
       </c>
       <c r="B8" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*B$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A8*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>44878.566884904</v>
+        <f aca="false">Scenarios!$E$21*B$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A8*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>34751.841884904</v>
       </c>
       <c r="C8" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*C$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A8*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>45350.526884904</v>
+        <f aca="false">Scenarios!$E$21*C$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A8*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>35184.471884904</v>
       </c>
       <c r="D8" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*D$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A8*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>46294.446884904</v>
+        <f aca="false">Scenarios!$E$21*D$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A8*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>36049.731884904</v>
       </c>
       <c r="E8" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*E$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A8*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>49126.206884904</v>
+        <f aca="false">Scenarios!$E$21*E$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A8*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>38645.511884904</v>
       </c>
       <c r="F8" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*F$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A8*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>53845.806884904</v>
+        <f aca="false">Scenarios!$E$21*F$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A8*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>42971.811884904</v>
       </c>
       <c r="G8" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*G$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A8*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>63285.006884904</v>
+        <f aca="false">Scenarios!$E$21*G$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A8*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>51624.411884904</v>
       </c>
       <c r="H8" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*H$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A8*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>91602.606884904</v>
+        <f aca="false">Scenarios!$E$21*H$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A8*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>77582.211884904</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7748,32 +8060,32 @@
         <v>20</v>
       </c>
       <c r="B9" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*B$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A9*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>45035.886884904</v>
+        <f aca="false">Scenarios!$E$21*B$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A9*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>34896.051884904</v>
       </c>
       <c r="C9" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*C$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A9*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>45665.166884904</v>
+        <f aca="false">Scenarios!$E$21*C$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A9*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>35472.891884904</v>
       </c>
       <c r="D9" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*D$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A9*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>46923.726884904</v>
+        <f aca="false">Scenarios!$E$21*D$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A9*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>36626.571884904</v>
       </c>
       <c r="E9" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*E$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A9*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>50699.406884904</v>
+        <f aca="false">Scenarios!$E$21*E$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A9*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>40087.611884904</v>
       </c>
       <c r="F9" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*F$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A9*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>56992.206884904</v>
+        <f aca="false">Scenarios!$E$21*F$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A9*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>45856.011884904</v>
       </c>
       <c r="G9" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*G$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A9*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>69577.806884904</v>
+        <f aca="false">Scenarios!$E$21*G$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A9*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>57392.811884904</v>
       </c>
       <c r="H9" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*H$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A9*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>107334.606884904</v>
+        <f aca="false">Scenarios!$E$21*H$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A9*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>92003.211884904</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7781,32 +8093,32 @@
         <v>25</v>
       </c>
       <c r="B10" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*B$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A10*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>45193.206884904</v>
+        <f aca="false">Scenarios!$E$21*B$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A10*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>35040.261884904</v>
       </c>
       <c r="C10" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*C$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A10*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>45979.806884904</v>
+        <f aca="false">Scenarios!$E$21*C$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A10*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>35761.311884904</v>
       </c>
       <c r="D10" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*D$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A10*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>47553.006884904</v>
+        <f aca="false">Scenarios!$E$21*D$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A10*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>37203.411884904</v>
       </c>
       <c r="E10" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*E$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A10*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>52272.606884904</v>
+        <f aca="false">Scenarios!$E$21*E$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A10*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>41529.711884904</v>
       </c>
       <c r="F10" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*F$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A10*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>60138.606884904</v>
+        <f aca="false">Scenarios!$E$21*F$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A10*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>48740.211884904</v>
       </c>
       <c r="G10" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*G$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A10*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>75870.606884904</v>
+        <f aca="false">Scenarios!$E$21*G$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A10*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>63161.211884904</v>
       </c>
       <c r="H10" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*H$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A10*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>123066.606884904</v>
+        <f aca="false">Scenarios!$E$21*H$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A10*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>106424.211884904</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7814,32 +8126,32 @@
         <v>30</v>
       </c>
       <c r="B11" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*B$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A11*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>45350.526884904</v>
+        <f aca="false">Scenarios!$E$21*B$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A11*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>35184.471884904</v>
       </c>
       <c r="C11" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*C$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A11*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>46294.446884904</v>
+        <f aca="false">Scenarios!$E$21*C$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A11*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>36049.731884904</v>
       </c>
       <c r="D11" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*D$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A11*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>48182.286884904</v>
+        <f aca="false">Scenarios!$E$21*D$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A11*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>37780.251884904</v>
       </c>
       <c r="E11" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*E$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A11*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>53845.806884904</v>
+        <f aca="false">Scenarios!$E$21*E$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A11*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>42971.811884904</v>
       </c>
       <c r="F11" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*F$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A11*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>63285.006884904</v>
+        <f aca="false">Scenarios!$E$21*F$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A11*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>51624.411884904</v>
       </c>
       <c r="G11" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*G$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A11*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>82163.406884904</v>
+        <f aca="false">Scenarios!$E$21*G$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A11*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>68929.611884904</v>
       </c>
       <c r="H11" s="25" t="n">
-        <f aca="false">Scenarios!$E$21*H$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*$A11*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
-        <v>138798.606884904</v>
+        <f aca="false">Scenarios!$E$21*H$4*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*$A11*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)+(Scenarios!E44-Scenarios!E38)-Scenarios!$E$33</f>
+        <v>120845.211884904</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7864,7 +8176,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -7876,10 +8188,10 @@
     </row>
     <row r="15" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -7893,8 +8205,8 @@
         <v>5</v>
       </c>
       <c r="B16" s="23" t="n">
-        <f aca="false">IFERROR((Scenarios!$E$33-(Scenarios!E44-Scenarios!E38))/(Scenarios!$E$21*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*A16*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)),0)</f>
-        <v>-7056.73259676201</v>
+        <f aca="false">IFERROR((Scenarios!$E$33-(Scenarios!E44-Scenarios!E38))/(Scenarios!$E$21*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*A16*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)),0)</f>
+        <v>-5949.52012428126</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -7908,8 +8220,8 @@
         <v>8</v>
       </c>
       <c r="B17" s="23" t="n">
-        <f aca="false">IFERROR((Scenarios!$E$33-(Scenarios!E44-Scenarios!E38))/(Scenarios!$E$21*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*A17*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)),0)</f>
-        <v>-4410.45787297626</v>
+        <f aca="false">IFERROR((Scenarios!$E$33-(Scenarios!E44-Scenarios!E38))/(Scenarios!$E$21*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*A17*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)),0)</f>
+        <v>-3718.45007767579</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -7923,8 +8235,8 @@
         <v>10</v>
       </c>
       <c r="B18" s="23" t="n">
-        <f aca="false">IFERROR((Scenarios!$E$33-(Scenarios!E44-Scenarios!E38))/(Scenarios!$E$21*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*A18*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)),0)</f>
-        <v>-3528.36629838101</v>
+        <f aca="false">IFERROR((Scenarios!$E$33-(Scenarios!E44-Scenarios!E38))/(Scenarios!$E$21*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*A18*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)),0)</f>
+        <v>-2974.76006214063</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -7938,8 +8250,8 @@
         <v>15</v>
       </c>
       <c r="B19" s="23" t="n">
-        <f aca="false">IFERROR((Scenarios!$E$33-(Scenarios!E44-Scenarios!E38))/(Scenarios!$E$21*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*A19*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)),0)</f>
-        <v>-2352.24419892067</v>
+        <f aca="false">IFERROR((Scenarios!$E$33-(Scenarios!E44-Scenarios!E38))/(Scenarios!$E$21*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*A19*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)),0)</f>
+        <v>-1983.17337476042</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -7953,8 +8265,8 @@
         <v>20</v>
       </c>
       <c r="B20" s="23" t="n">
-        <f aca="false">IFERROR((Scenarios!$E$33-(Scenarios!E44-Scenarios!E38))/(Scenarios!$E$21*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*A20*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)),0)</f>
-        <v>-1764.1831491905</v>
+        <f aca="false">IFERROR((Scenarios!$E$33-(Scenarios!E44-Scenarios!E38))/(Scenarios!$E$21*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*A20*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)),0)</f>
+        <v>-1487.38003107031</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -7968,8 +8280,8 @@
         <v>25</v>
       </c>
       <c r="B21" s="23" t="n">
-        <f aca="false">IFERROR((Scenarios!$E$33-(Scenarios!E44-Scenarios!E38))/(Scenarios!$E$21*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*A21*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)),0)</f>
-        <v>-1411.3465193524</v>
+        <f aca="false">IFERROR((Scenarios!$E$33-(Scenarios!E44-Scenarios!E38))/(Scenarios!$E$21*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*A21*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)),0)</f>
+        <v>-1189.90402485625</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -7983,8 +8295,8 @@
         <v>30</v>
       </c>
       <c r="B22" s="23" t="n">
-        <f aca="false">IFERROR((Scenarios!$E$33-(Scenarios!E44-Scenarios!E38))/(Scenarios!$E$21*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$41:$F$47)/MAX(1,Scenarios!E21))/1000*A22*INDEX(Assumptions!$B$74:$D$74,Assumptions!$B$5)*INDEX(Assumptions!$B$75:$D$75,Assumptions!$B$5)),0)</f>
-        <v>-1176.12209946034</v>
+        <f aca="false">IFERROR((Scenarios!$E$33-(Scenarios!E44-Scenarios!E38))/(Scenarios!$E$21*(SUMPRODUCT(Scenarios!E14:E20,Assumptions!$F$43:$F$49)/MAX(1,Scenarios!E21))/1000*A22*INDEX(Assumptions!$B$78:$D$78,Assumptions!$B$5)*INDEX(Assumptions!$B$79:$D$79,Assumptions!$B$5)),0)</f>
+        <v>-991.586687380209</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -8018,13 +8330,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="B1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="B2" s="2"/>
     </row>
@@ -8034,66 +8346,66 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
